--- a/output7/【河洛文讀注音-雅俗通】《詩經 小雅 鹿鳴》.xlsx
+++ b/output7/【河洛文讀注音-雅俗通】《詩經 小雅 鹿鳴》.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0AEC3E2-AC99-4243-8269-791416DCD4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3742248A-2B83-4D83-B5A2-F3039E2F7CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="718" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
-    <sheet name="缺字表" sheetId="430" r:id="rId2"/>
-    <sheet name="標音字庫" sheetId="429" r:id="rId3"/>
-    <sheet name="人工標音字庫" sheetId="428" r:id="rId4"/>
+    <sheet name="缺字表" sheetId="433" r:id="rId2"/>
+    <sheet name="標音字庫" sheetId="432" r:id="rId3"/>
+    <sheet name="人工標音字庫" sheetId="431" r:id="rId4"/>
     <sheet name="漢字注音" sheetId="9" r:id="rId5"/>
   </sheets>
   <definedNames>
@@ -1355,14 +1355,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hing5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>經五喜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>上及右</t>
   </si>
   <si>
@@ -1370,6 +1362,14 @@
   </si>
   <si>
     <t>Iu1-Iu1-Lok4-Bing5_001.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hang5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江五喜</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1761,7 +1761,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1897,28 +1897,7 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="7">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="7" applyFont="1">
@@ -1932,6 +1911,44 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="2" borderId="3" xfId="5" applyNumberFormat="1" applyFill="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -2382,7 +2399,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D7" s="36"/>
       <c r="E7" s="36"/>
@@ -2470,7 +2487,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="30">
@@ -2478,7 +2495,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30">
@@ -2524,7 +2541,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79105FA-27CD-4D54-9D2A-6947AF69012C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DEF6B94-989F-439E-87E8-9D3ED6B9E0C7}">
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
@@ -2549,7 +2566,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6102FB6-3117-4254-B85D-F33990B08999}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52A8BD00-0BC8-4A12-9EAC-883D07A58FD5}">
   <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
@@ -3344,7 +3361,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15F4F3BA-3C27-436D-8069-87BBD1B36746}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{141BEAF5-F093-4160-9C49-016D91FAF12D}">
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
@@ -3377,7 +3394,7 @@
     <col min="2" max="2" width="7.25" style="5" customWidth="1"/>
     <col min="3" max="3" width="4.625" style="5" customWidth="1"/>
     <col min="4" max="18" width="28.5" style="42" customWidth="1"/>
-    <col min="19" max="19" width="4.625" style="6" customWidth="1"/>
+    <col min="19" max="19" width="4.625" style="53" customWidth="1"/>
     <col min="20" max="20" width="3.5" style="5" customWidth="1"/>
     <col min="21" max="21" width="23.5" style="5" customWidth="1"/>
     <col min="22" max="22" width="89.625" style="7" customWidth="1"/>
@@ -3475,7 +3492,7 @@
       <c r="P2" s="40"/>
       <c r="Q2" s="40"/>
       <c r="R2" s="40"/>
-      <c r="S2" s="45"/>
+      <c r="S2" s="54"/>
       <c r="V2" s="9">
         <f xml:space="preserve"> LEN(V3)</f>
         <v>141</v>
@@ -3484,37 +3501,37 @@
     <row r="3" spans="1:22" s="12" customFormat="1" ht="60" customHeight="1">
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
-      <c r="D3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" s="41" t="s">
+      <c r="D3" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="51" t="s">
         <v>32</v>
       </c>
       <c r="O3" s="41" t="s">
@@ -3529,47 +3546,47 @@
       <c r="R3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S3" s="52" t="s">
+      <c r="S3" s="55" t="s">
         <v>32</v>
       </c>
       <c r="T3" s="13"/>
-      <c r="V3" s="54" t="s">
+      <c r="V3" s="47" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B4" s="14"/>
-      <c r="D4" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="43" t="s">
+      <c r="D4" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="52" t="s">
         <v>206</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="52" t="s">
         <v>209</v>
       </c>
-      <c r="G4" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="43" t="s">
+      <c r="G4" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="52" t="s">
         <v>212</v>
       </c>
-      <c r="I4" s="43" t="s">
+      <c r="I4" s="52" t="s">
         <v>215</v>
       </c>
-      <c r="J4" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="43" t="s">
+      <c r="J4" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="52" t="s">
         <v>218</v>
       </c>
-      <c r="L4" s="43" t="s">
+      <c r="L4" s="52" t="s">
         <v>221</v>
       </c>
-      <c r="M4" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" s="43" t="s">
+      <c r="M4" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="52" t="s">
         <v>32</v>
       </c>
       <c r="O4" s="43" t="s">
@@ -3584,46 +3601,46 @@
       <c r="R4" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S4" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V4" s="55"/>
+      <c r="S4" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V4" s="48"/>
     </row>
     <row r="5" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="15">
         <v>1</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="F5" s="44" t="s">
+      <c r="F5" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="G5" s="44" t="s">
+      <c r="G5" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H5" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="I5" s="44" t="s">
+      <c r="I5" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="J5" s="44" t="s">
+      <c r="J5" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="K5" s="44" t="s">
+      <c r="K5" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="L5" s="44" t="s">
+      <c r="L5" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="M5" s="44" t="s">
+      <c r="M5" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="N5" s="44" t="str">
+      <c r="N5" s="50" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -3640,45 +3657,45 @@
       <c r="R5" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S5" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V5" s="55"/>
+      <c r="S5" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V5" s="48"/>
     </row>
     <row r="6" spans="1:22" s="18" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="16"/>
       <c r="C6" s="17"/>
-      <c r="D6" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="43" t="s">
+      <c r="D6" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="52" t="s">
         <v>207</v>
       </c>
-      <c r="F6" s="43" t="s">
+      <c r="F6" s="52" t="s">
         <v>210</v>
       </c>
-      <c r="G6" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="43" t="s">
+      <c r="G6" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="52" t="s">
         <v>213</v>
       </c>
-      <c r="I6" s="43" t="s">
+      <c r="I6" s="52" t="s">
         <v>216</v>
       </c>
-      <c r="J6" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="43" t="s">
+      <c r="J6" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="52" t="s">
         <v>219</v>
       </c>
-      <c r="L6" s="43" t="s">
+      <c r="L6" s="52" t="s">
         <v>222</v>
       </c>
-      <c r="M6" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N6" s="43" t="s">
+      <c r="M6" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="52" t="s">
         <v>32</v>
       </c>
       <c r="O6" s="43" t="s">
@@ -3693,470 +3710,470 @@
       <c r="R6" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S6" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="V6" s="55"/>
+      <c r="S6" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="V6" s="48"/>
     </row>
     <row r="7" spans="1:22" s="22" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="19"/>
       <c r="C7" s="20"/>
-      <c r="D7" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="N7" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="P7" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q7" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="R7" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="S7" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="V7" s="55"/>
+      <c r="D7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="S7" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="V7" s="48"/>
     </row>
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="14"/>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="52" t="s">
         <v>227</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="52" t="s">
         <v>227</v>
       </c>
-      <c r="F8" s="43" t="s">
+      <c r="F8" s="52" t="s">
         <v>218</v>
       </c>
-      <c r="G8" s="43" t="s">
+      <c r="G8" s="52" t="s">
         <v>221</v>
       </c>
-      <c r="H8" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="43" t="s">
+      <c r="H8" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="52" t="s">
         <v>230</v>
       </c>
-      <c r="J8" s="43" t="s">
+      <c r="J8" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="K8" s="43" t="s">
+      <c r="K8" s="52" t="s">
         <v>233</v>
       </c>
-      <c r="L8" s="43" t="s">
+      <c r="L8" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="M8" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" s="43" t="s">
+      <c r="M8" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="O8" s="43" t="s">
+      <c r="O8" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="P8" s="43" t="s">
+      <c r="P8" s="52" t="s">
         <v>242</v>
       </c>
-      <c r="Q8" s="43" t="s">
+      <c r="Q8" s="52" t="s">
         <v>245</v>
       </c>
-      <c r="R8" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="S8" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V8" s="55"/>
+      <c r="R8" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="S8" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V8" s="48"/>
     </row>
     <row r="9" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="15">
         <f>B5+1</f>
         <v>2</v>
       </c>
-      <c r="D9" s="44" t="s">
+      <c r="D9" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="F9" s="44" t="s">
+      <c r="F9" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="G9" s="44" t="s">
+      <c r="G9" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="44" t="s">
+      <c r="I9" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="J9" s="44" t="s">
+      <c r="J9" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="K9" s="44" t="s">
+      <c r="K9" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="L9" s="44" t="s">
+      <c r="L9" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="M9" s="44" t="s">
+      <c r="M9" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="44" t="s">
+      <c r="N9" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="O9" s="44" t="s">
+      <c r="O9" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="P9" s="44" t="s">
+      <c r="P9" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="Q9" s="44" t="s">
+      <c r="Q9" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="R9" s="44" t="s">
+      <c r="R9" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="47" t="s">
+      <c r="S9" s="57" t="s">
         <v>32</v>
       </c>
       <c r="T9" s="13"/>
-      <c r="V9" s="55"/>
+      <c r="V9" s="48"/>
     </row>
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="16"/>
-      <c r="D10" s="43" t="s">
+      <c r="D10" s="52" t="s">
         <v>228</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="52" t="s">
         <v>228</v>
       </c>
-      <c r="F10" s="43" t="s">
+      <c r="F10" s="52" t="s">
         <v>219</v>
       </c>
-      <c r="G10" s="43" t="s">
+      <c r="G10" s="52" t="s">
         <v>222</v>
       </c>
-      <c r="H10" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="43" t="s">
+      <c r="H10" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="52" t="s">
         <v>231</v>
       </c>
-      <c r="J10" s="43" t="s">
+      <c r="J10" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="K10" s="43" t="s">
+      <c r="K10" s="52" t="s">
         <v>234</v>
       </c>
-      <c r="L10" s="43" t="s">
+      <c r="L10" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="M10" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N10" s="43" t="s">
+      <c r="M10" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="52" t="s">
         <v>237</v>
       </c>
-      <c r="O10" s="43" t="s">
+      <c r="O10" s="52" t="s">
         <v>240</v>
       </c>
-      <c r="P10" s="43" t="s">
+      <c r="P10" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="Q10" s="43" t="s">
+      <c r="Q10" s="52" t="s">
         <v>246</v>
       </c>
-      <c r="R10" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="S10" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V10" s="55"/>
+      <c r="R10" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V10" s="48"/>
     </row>
     <row r="11" spans="1:22" s="21" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="23"/>
       <c r="C11" s="24"/>
-      <c r="D11" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="L11" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="M11" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="N11" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="O11" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="P11" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q11" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="R11" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="S11" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="V11" s="55"/>
+      <c r="D11" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="O11" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q11" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="S11" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="V11" s="48"/>
     </row>
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="14"/>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="52" t="s">
         <v>248</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="43" t="s">
+      <c r="F12" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="G12" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="43" t="s">
+      <c r="H12" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="J12" s="43" t="s">
+      <c r="J12" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="43" t="s">
+      <c r="K12" s="52" t="s">
         <v>248</v>
       </c>
-      <c r="L12" s="43" t="s">
+      <c r="L12" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="M12" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N12" s="43" t="s">
+      <c r="M12" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" s="52" t="s">
         <v>251</v>
       </c>
-      <c r="O12" s="43" t="s">
+      <c r="O12" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="P12" s="43" t="s">
+      <c r="P12" s="52" t="s">
         <v>254</v>
       </c>
-      <c r="Q12" s="43" t="s">
+      <c r="Q12" s="52" t="s">
         <v>257</v>
       </c>
-      <c r="R12" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="S12" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V12" s="55"/>
+      <c r="R12" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="S12" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V12" s="48"/>
     </row>
     <row r="13" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="15">
         <f>B9+1</f>
         <v>3</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="E13" s="44" t="s">
+      <c r="E13" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="44" t="s">
+      <c r="F13" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="44" t="s">
+      <c r="G13" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="I13" s="44" t="s">
+      <c r="I13" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="J13" s="44" t="s">
+      <c r="J13" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="K13" s="44" t="s">
+      <c r="K13" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="L13" s="44" t="s">
+      <c r="L13" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="M13" s="44" t="s">
+      <c r="M13" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="N13" s="44" t="s">
+      <c r="N13" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="O13" s="44" t="s">
+      <c r="O13" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="P13" s="44" t="s">
+      <c r="P13" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="Q13" s="44" t="s">
+      <c r="Q13" s="50" t="s">
         <v>148</v>
       </c>
-      <c r="R13" s="44" t="s">
+      <c r="R13" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="S13" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V13" s="55"/>
+      <c r="S13" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V13" s="48"/>
     </row>
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="16"/>
-      <c r="D14" s="43" t="s">
+      <c r="D14" s="52" t="s">
         <v>249</v>
       </c>
-      <c r="E14" s="43" t="s">
+      <c r="E14" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="43" t="s">
+      <c r="F14" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G14" s="43" t="s">
+      <c r="G14" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="H14" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="43" t="s">
+      <c r="H14" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="J14" s="43" t="s">
+      <c r="J14" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="K14" s="43" t="s">
+      <c r="K14" s="52" t="s">
         <v>249</v>
       </c>
-      <c r="L14" s="43" t="s">
+      <c r="L14" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="M14" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N14" s="43" t="s">
+      <c r="M14" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" s="52" t="s">
         <v>252</v>
       </c>
-      <c r="O14" s="43" t="s">
+      <c r="O14" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="P14" s="43" t="s">
+      <c r="P14" s="52" t="s">
         <v>255</v>
       </c>
-      <c r="Q14" s="43" t="s">
+      <c r="Q14" s="52" t="s">
         <v>258</v>
       </c>
-      <c r="R14" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="S14" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V14" s="55"/>
+      <c r="R14" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="S14" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V14" s="48"/>
     </row>
     <row r="15" spans="1:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="10"/>
       <c r="C15" s="25"/>
-      <c r="D15" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H15" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="J15" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="L15" s="41" t="s">
-        <v>366</v>
-      </c>
-      <c r="M15" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="N15" s="41" t="s">
+      <c r="D15" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" s="51" t="s">
         <v>32</v>
       </c>
       <c r="O15" s="41" t="s">
@@ -4171,44 +4188,44 @@
       <c r="R15" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S15" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V15" s="55"/>
+      <c r="S15" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V15" s="48"/>
     </row>
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="14"/>
-      <c r="D16" s="43" t="s">
+      <c r="D16" s="52" t="s">
         <v>262</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="E16" s="52" t="s">
         <v>233</v>
       </c>
-      <c r="F16" s="43" t="s">
+      <c r="F16" s="52" t="s">
         <v>265</v>
       </c>
-      <c r="G16" s="43" t="s">
+      <c r="G16" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="H16" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="43" t="s">
+      <c r="H16" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="52" t="s">
         <v>268</v>
       </c>
-      <c r="J16" s="43" t="s">
+      <c r="J16" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="K16" s="43" t="s">
+      <c r="K16" s="52" t="s">
         <v>271</v>
       </c>
-      <c r="L16" s="43" t="s">
-        <v>366</v>
-      </c>
-      <c r="M16" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N16" s="43" t="s">
+      <c r="L16" s="52" t="s">
+        <v>369</v>
+      </c>
+      <c r="M16" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N16" s="52" t="s">
         <v>32</v>
       </c>
       <c r="O16" s="43" t="s">
@@ -4223,47 +4240,47 @@
       <c r="R16" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S16" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V16" s="55"/>
+      <c r="S16" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V16" s="48"/>
     </row>
     <row r="17" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="15">
         <f>B13+1</f>
         <v>4</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D17" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="E17" s="44" t="s">
+      <c r="E17" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="F17" s="44" t="s">
+      <c r="F17" s="50" t="s">
         <v>152</v>
       </c>
-      <c r="G17" s="44" t="s">
+      <c r="G17" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="44" t="s">
+      <c r="I17" s="50" t="s">
         <v>154</v>
       </c>
-      <c r="J17" s="44" t="s">
+      <c r="J17" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="K17" s="44" t="s">
+      <c r="K17" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="L17" s="44" t="s">
+      <c r="L17" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="M17" s="44" t="s">
+      <c r="M17" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="N17" s="44" t="str">
+      <c r="N17" s="50" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -4280,44 +4297,44 @@
       <c r="R17" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S17" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V17" s="55"/>
+      <c r="S17" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V17" s="48"/>
     </row>
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="16"/>
-      <c r="D18" s="43" t="s">
+      <c r="D18" s="52" t="s">
         <v>263</v>
       </c>
-      <c r="E18" s="43" t="s">
+      <c r="E18" s="52" t="s">
         <v>234</v>
       </c>
-      <c r="F18" s="43" t="s">
+      <c r="F18" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="G18" s="43" t="s">
+      <c r="G18" s="52" t="s">
         <v>237</v>
       </c>
-      <c r="H18" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="43" t="s">
+      <c r="H18" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="52" t="s">
         <v>269</v>
       </c>
-      <c r="J18" s="43" t="s">
+      <c r="J18" s="52" t="s">
         <v>237</v>
       </c>
-      <c r="K18" s="43" t="s">
+      <c r="K18" s="52" t="s">
         <v>272</v>
       </c>
-      <c r="L18" s="43" t="s">
-        <v>367</v>
-      </c>
-      <c r="M18" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N18" s="43" t="s">
+      <c r="L18" s="52" t="s">
+        <v>370</v>
+      </c>
+      <c r="M18" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N18" s="52" t="s">
         <v>32</v>
       </c>
       <c r="O18" s="43" t="s">
@@ -4332,1227 +4349,1227 @@
       <c r="R18" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S18" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V18" s="55"/>
+      <c r="S18" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V18" s="48"/>
     </row>
     <row r="19" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="10"/>
       <c r="C19" s="25"/>
-      <c r="D19" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H19" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="J19" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K19" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="L19" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="M19" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="N19" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="O19" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="P19" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q19" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="R19" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="S19" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V19" s="55"/>
+      <c r="D19" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="N19" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="O19" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="P19" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q19" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="S19" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V19" s="48"/>
     </row>
     <row r="20" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="14"/>
-      <c r="D20" s="43" t="s">
+      <c r="D20" s="52" t="s">
         <v>227</v>
       </c>
-      <c r="E20" s="43" t="s">
+      <c r="E20" s="52" t="s">
         <v>227</v>
       </c>
-      <c r="F20" s="43" t="s">
+      <c r="F20" s="52" t="s">
         <v>218</v>
       </c>
-      <c r="G20" s="43" t="s">
+      <c r="G20" s="52" t="s">
         <v>221</v>
       </c>
-      <c r="H20" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="43" t="s">
+      <c r="H20" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="52" t="s">
         <v>230</v>
       </c>
-      <c r="J20" s="43" t="s">
+      <c r="J20" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="K20" s="43" t="s">
+      <c r="K20" s="52" t="s">
         <v>233</v>
       </c>
-      <c r="L20" s="43" t="s">
+      <c r="L20" s="52" t="s">
         <v>278</v>
       </c>
-      <c r="M20" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N20" s="43" t="s">
+      <c r="M20" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="O20" s="43" t="s">
+      <c r="O20" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="P20" s="43" t="s">
+      <c r="P20" s="52" t="s">
         <v>242</v>
       </c>
-      <c r="Q20" s="43" t="s">
+      <c r="Q20" s="52" t="s">
         <v>245</v>
       </c>
-      <c r="R20" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="S20" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V20" s="55"/>
+      <c r="R20" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="S20" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V20" s="48"/>
     </row>
     <row r="21" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="15">
         <f>B17+1</f>
         <v>5</v>
       </c>
-      <c r="D21" s="44" t="s">
+      <c r="D21" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="E21" s="44" t="s">
+      <c r="E21" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="F21" s="44" t="s">
+      <c r="F21" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="G21" s="44" t="s">
+      <c r="G21" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="H21" s="44" t="s">
+      <c r="H21" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="I21" s="44" t="s">
+      <c r="I21" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="J21" s="44" t="s">
+      <c r="J21" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="K21" s="44" t="s">
+      <c r="K21" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="L21" s="44" t="s">
+      <c r="L21" s="50" t="s">
         <v>158</v>
       </c>
-      <c r="M21" s="44" t="s">
+      <c r="M21" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="N21" s="44" t="s">
+      <c r="N21" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="O21" s="44" t="s">
+      <c r="O21" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="P21" s="44" t="s">
+      <c r="P21" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="Q21" s="44" t="s">
+      <c r="Q21" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="R21" s="44" t="s">
+      <c r="R21" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="S21" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V21" s="55"/>
+      <c r="S21" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V21" s="48"/>
     </row>
     <row r="22" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="16"/>
-      <c r="D22" s="43" t="s">
+      <c r="D22" s="52" t="s">
         <v>228</v>
       </c>
-      <c r="E22" s="43" t="s">
+      <c r="E22" s="52" t="s">
         <v>228</v>
       </c>
-      <c r="F22" s="43" t="s">
+      <c r="F22" s="52" t="s">
         <v>219</v>
       </c>
-      <c r="G22" s="43" t="s">
+      <c r="G22" s="52" t="s">
         <v>222</v>
       </c>
-      <c r="H22" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="43" t="s">
+      <c r="H22" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="52" t="s">
         <v>231</v>
       </c>
-      <c r="J22" s="43" t="s">
+      <c r="J22" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="K22" s="43" t="s">
+      <c r="K22" s="52" t="s">
         <v>234</v>
       </c>
-      <c r="L22" s="43" t="s">
+      <c r="L22" s="52" t="s">
         <v>279</v>
       </c>
-      <c r="M22" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N22" s="43" t="s">
+      <c r="M22" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" s="52" t="s">
         <v>237</v>
       </c>
-      <c r="O22" s="43" t="s">
+      <c r="O22" s="52" t="s">
         <v>240</v>
       </c>
-      <c r="P22" s="43" t="s">
+      <c r="P22" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="Q22" s="43" t="s">
+      <c r="Q22" s="52" t="s">
         <v>246</v>
       </c>
-      <c r="R22" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="S22" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V22" s="55"/>
+      <c r="R22" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="S22" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V22" s="48"/>
     </row>
     <row r="23" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="10"/>
       <c r="C23" s="25"/>
-      <c r="D23" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="J23" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K23" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="L23" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="M23" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="N23" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="O23" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="P23" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q23" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="R23" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="S23" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V23" s="55"/>
+      <c r="D23" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="N23" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="P23" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q23" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="R23" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="S23" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V23" s="48"/>
     </row>
     <row r="24" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="14"/>
-      <c r="D24" s="43" t="s">
+      <c r="D24" s="52" t="s">
         <v>281</v>
       </c>
-      <c r="E24" s="43" t="s">
+      <c r="E24" s="52" t="s">
         <v>284</v>
       </c>
-      <c r="F24" s="43" t="s">
+      <c r="F24" s="52" t="s">
         <v>287</v>
       </c>
-      <c r="G24" s="43" t="s">
+      <c r="G24" s="52" t="s">
         <v>290</v>
       </c>
-      <c r="H24" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="43" t="s">
+      <c r="H24" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="52" t="s">
         <v>268</v>
       </c>
-      <c r="J24" s="43" t="s">
+      <c r="J24" s="52" t="s">
         <v>293</v>
       </c>
-      <c r="K24" s="43" t="s">
+      <c r="K24" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="L24" s="43" t="s">
+      <c r="L24" s="52" t="s">
         <v>296</v>
       </c>
-      <c r="M24" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N24" s="43" t="s">
+      <c r="M24" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" s="52" t="s">
         <v>299</v>
       </c>
-      <c r="O24" s="43" t="s">
+      <c r="O24" s="52" t="s">
         <v>302</v>
       </c>
-      <c r="P24" s="43" t="s">
+      <c r="P24" s="52" t="s">
         <v>254</v>
       </c>
-      <c r="Q24" s="43" t="s">
+      <c r="Q24" s="52" t="s">
         <v>305</v>
       </c>
-      <c r="R24" s="43" t="s">
+      <c r="R24" s="52" t="s">
         <v>254</v>
       </c>
-      <c r="S24" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V24" s="55"/>
+      <c r="S24" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V24" s="48"/>
     </row>
     <row r="25" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B25" s="15">
         <f>B21+1</f>
         <v>6</v>
       </c>
-      <c r="D25" s="44" t="s">
+      <c r="D25" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="E25" s="44" t="s">
+      <c r="E25" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="F25" s="44" t="s">
+      <c r="F25" s="50" t="s">
         <v>164</v>
       </c>
-      <c r="G25" s="44" t="s">
+      <c r="G25" s="50" t="s">
         <v>166</v>
       </c>
-      <c r="H25" s="44" t="s">
+      <c r="H25" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="I25" s="44" t="s">
+      <c r="I25" s="50" t="s">
         <v>168</v>
       </c>
-      <c r="J25" s="44" t="s">
+      <c r="J25" s="50" t="s">
         <v>170</v>
       </c>
-      <c r="K25" s="44" t="s">
+      <c r="K25" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="L25" s="44" t="s">
+      <c r="L25" s="50" t="s">
         <v>172</v>
       </c>
-      <c r="M25" s="44" t="s">
+      <c r="M25" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="N25" s="44" t="s">
+      <c r="N25" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="O25" s="44" t="s">
+      <c r="O25" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="P25" s="44" t="s">
+      <c r="P25" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="Q25" s="44" t="s">
+      <c r="Q25" s="50" t="s">
         <v>178</v>
       </c>
-      <c r="R25" s="44" t="s">
+      <c r="R25" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="S25" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V25" s="55"/>
+      <c r="S25" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V25" s="48"/>
     </row>
     <row r="26" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="16"/>
-      <c r="D26" s="43" t="s">
+      <c r="D26" s="52" t="s">
         <v>282</v>
       </c>
-      <c r="E26" s="43" t="s">
+      <c r="E26" s="52" t="s">
         <v>285</v>
       </c>
-      <c r="F26" s="43" t="s">
+      <c r="F26" s="52" t="s">
         <v>288</v>
       </c>
-      <c r="G26" s="43" t="s">
+      <c r="G26" s="52" t="s">
         <v>291</v>
       </c>
-      <c r="H26" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="43" t="s">
+      <c r="H26" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="52" t="s">
         <v>269</v>
       </c>
-      <c r="J26" s="43" t="s">
+      <c r="J26" s="52" t="s">
         <v>294</v>
       </c>
-      <c r="K26" s="43" t="s">
+      <c r="K26" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="L26" s="43" t="s">
+      <c r="L26" s="52" t="s">
         <v>297</v>
       </c>
-      <c r="M26" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N26" s="43" t="s">
+      <c r="M26" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N26" s="52" t="s">
         <v>300</v>
       </c>
-      <c r="O26" s="43" t="s">
+      <c r="O26" s="52" t="s">
         <v>303</v>
       </c>
-      <c r="P26" s="43" t="s">
+      <c r="P26" s="52" t="s">
         <v>255</v>
       </c>
-      <c r="Q26" s="43" t="s">
+      <c r="Q26" s="52" t="s">
         <v>306</v>
       </c>
-      <c r="R26" s="43" t="s">
+      <c r="R26" s="52" t="s">
         <v>255</v>
       </c>
-      <c r="S26" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V26" s="55"/>
+      <c r="S26" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V26" s="48"/>
     </row>
     <row r="27" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B27" s="10"/>
       <c r="C27" s="25"/>
-      <c r="D27" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H27" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="J27" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K27" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="L27" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="M27" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="N27" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="O27" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="P27" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q27" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="R27" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="S27" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V27" s="55"/>
+      <c r="D27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="M27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="N27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="O27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="P27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="R27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="S27" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V27" s="48"/>
     </row>
     <row r="28" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="14"/>
-      <c r="D28" s="43" t="s">
+      <c r="D28" s="52" t="s">
         <v>320</v>
       </c>
-      <c r="E28" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="43" t="s">
+      <c r="E28" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="G28" s="43" t="s">
+      <c r="G28" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="H28" s="43" t="s">
+      <c r="H28" s="52" t="s">
         <v>323</v>
       </c>
-      <c r="I28" s="43" t="s">
+      <c r="I28" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="J28" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="K28" s="43" t="s">
+      <c r="J28" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" s="52" t="s">
         <v>242</v>
       </c>
-      <c r="L28" s="43" t="s">
+      <c r="L28" s="52" t="s">
         <v>245</v>
       </c>
-      <c r="M28" s="43" t="s">
+      <c r="M28" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="43" t="s">
+      <c r="N28" s="52" t="s">
         <v>88</v>
       </c>
-      <c r="O28" s="43" t="s">
+      <c r="O28" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="P28" s="43" t="s">
+      <c r="P28" s="52" t="s">
         <v>326</v>
       </c>
-      <c r="Q28" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="R28" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="S28" s="46" t="s">
+      <c r="Q28" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="R28" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="S28" s="56" t="s">
         <v>32</v>
       </c>
       <c r="U28" s="26"/>
-      <c r="V28" s="55"/>
+      <c r="V28" s="48"/>
     </row>
     <row r="29" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B29" s="15">
         <f>B25+1</f>
         <v>7</v>
       </c>
-      <c r="D29" s="44" t="s">
+      <c r="D29" s="50" t="s">
         <v>180</v>
       </c>
-      <c r="E29" s="44" t="s">
+      <c r="E29" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="F29" s="44" t="s">
+      <c r="F29" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="G29" s="44" t="s">
+      <c r="G29" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="H29" s="44" t="s">
+      <c r="H29" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="I29" s="44" t="s">
+      <c r="I29" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="J29" s="44" t="s">
+      <c r="J29" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="K29" s="44" t="s">
+      <c r="K29" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="L29" s="44" t="s">
+      <c r="L29" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="M29" s="44" t="s">
+      <c r="M29" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="N29" s="44" t="s">
+      <c r="N29" s="50" t="s">
         <v>186</v>
       </c>
-      <c r="O29" s="44" t="s">
+      <c r="O29" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="P29" s="44" t="s">
+      <c r="P29" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="Q29" s="44" t="s">
+      <c r="Q29" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="R29" s="44" t="str">
+      <c r="R29" s="50" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="S29" s="47" t="s">
+      <c r="S29" s="57" t="s">
         <v>32</v>
       </c>
       <c r="U29" s="26"/>
-      <c r="V29" s="55"/>
+      <c r="V29" s="48"/>
     </row>
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="16"/>
-      <c r="D30" s="43" t="s">
+      <c r="D30" s="52" t="s">
         <v>321</v>
       </c>
-      <c r="E30" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="43" t="s">
+      <c r="E30" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" s="52" t="s">
         <v>237</v>
       </c>
-      <c r="G30" s="43" t="s">
+      <c r="G30" s="52" t="s">
         <v>240</v>
       </c>
-      <c r="H30" s="43" t="s">
+      <c r="H30" s="52" t="s">
         <v>324</v>
       </c>
-      <c r="I30" s="43" t="s">
+      <c r="I30" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="J30" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="K30" s="43" t="s">
+      <c r="J30" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="K30" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="L30" s="43" t="s">
+      <c r="L30" s="52" t="s">
         <v>246</v>
       </c>
-      <c r="M30" s="43" t="s">
+      <c r="M30" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="N30" s="43" t="s">
+      <c r="N30" s="52" t="s">
         <v>89</v>
       </c>
-      <c r="O30" s="43" t="s">
+      <c r="O30" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="P30" s="43" t="s">
+      <c r="P30" s="52" t="s">
         <v>327</v>
       </c>
-      <c r="Q30" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="R30" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="S30" s="49" t="s">
+      <c r="Q30" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="R30" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="S30" s="60" t="s">
         <v>32</v>
       </c>
       <c r="U30" s="26"/>
-      <c r="V30" s="55"/>
+      <c r="V30" s="48"/>
     </row>
     <row r="31" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B31" s="10"/>
       <c r="C31" s="25"/>
-      <c r="D31" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G31" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H31" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="J31" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K31" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="L31" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="M31" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="N31" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="O31" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="P31" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q31" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="R31" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="S31" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V31" s="55"/>
+      <c r="D31" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J31" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="K31" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="M31" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="N31" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="O31" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="P31" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q31" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="S31" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V31" s="48"/>
     </row>
     <row r="32" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B32" s="14"/>
-      <c r="D32" s="43" t="s">
+      <c r="D32" s="52" t="s">
         <v>227</v>
       </c>
-      <c r="E32" s="43" t="s">
+      <c r="E32" s="52" t="s">
         <v>227</v>
       </c>
-      <c r="F32" s="43" t="s">
+      <c r="F32" s="52" t="s">
         <v>218</v>
       </c>
-      <c r="G32" s="43" t="s">
+      <c r="G32" s="52" t="s">
         <v>221</v>
       </c>
-      <c r="H32" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="43" t="s">
+      <c r="H32" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" s="52" t="s">
         <v>230</v>
       </c>
-      <c r="J32" s="43" t="s">
+      <c r="J32" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="K32" s="43" t="s">
+      <c r="K32" s="52" t="s">
         <v>233</v>
       </c>
-      <c r="L32" s="43" t="s">
+      <c r="L32" s="52" t="s">
         <v>329</v>
       </c>
-      <c r="M32" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N32" s="43" t="s">
+      <c r="M32" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N32" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="O32" s="43" t="s">
+      <c r="O32" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="P32" s="43" t="s">
+      <c r="P32" s="52" t="s">
         <v>242</v>
       </c>
-      <c r="Q32" s="43" t="s">
+      <c r="Q32" s="52" t="s">
         <v>245</v>
       </c>
-      <c r="R32" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="S32" s="46" t="s">
+      <c r="R32" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="S32" s="56" t="s">
         <v>32</v>
       </c>
       <c r="U32" s="26"/>
-      <c r="V32" s="55"/>
+      <c r="V32" s="48"/>
     </row>
     <row r="33" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B33" s="15">
         <f>B29+1</f>
         <v>8</v>
       </c>
-      <c r="D33" s="44" t="s">
+      <c r="D33" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="E33" s="44" t="s">
+      <c r="E33" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="F33" s="44" t="s">
+      <c r="F33" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="G33" s="44" t="s">
+      <c r="G33" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="H33" s="44" t="s">
+      <c r="H33" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="I33" s="44" t="s">
+      <c r="I33" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="J33" s="44" t="s">
+      <c r="J33" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="K33" s="44" t="s">
+      <c r="K33" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="L33" s="44" t="s">
+      <c r="L33" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="M33" s="44" t="s">
+      <c r="M33" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="N33" s="44" t="s">
+      <c r="N33" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="O33" s="44" t="s">
+      <c r="O33" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="P33" s="44" t="s">
+      <c r="P33" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="Q33" s="44" t="s">
+      <c r="Q33" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="R33" s="44" t="s">
+      <c r="R33" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="S33" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V33" s="55"/>
+      <c r="S33" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V33" s="48"/>
     </row>
     <row r="34" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B34" s="16"/>
-      <c r="D34" s="43" t="s">
+      <c r="D34" s="52" t="s">
         <v>228</v>
       </c>
-      <c r="E34" s="43" t="s">
+      <c r="E34" s="52" t="s">
         <v>228</v>
       </c>
-      <c r="F34" s="43" t="s">
+      <c r="F34" s="52" t="s">
         <v>219</v>
       </c>
-      <c r="G34" s="43" t="s">
+      <c r="G34" s="52" t="s">
         <v>222</v>
       </c>
-      <c r="H34" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="43" t="s">
+      <c r="H34" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="52" t="s">
         <v>231</v>
       </c>
-      <c r="J34" s="43" t="s">
+      <c r="J34" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="K34" s="43" t="s">
+      <c r="K34" s="52" t="s">
         <v>234</v>
       </c>
-      <c r="L34" s="43" t="s">
+      <c r="L34" s="52" t="s">
         <v>330</v>
       </c>
-      <c r="M34" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N34" s="43" t="s">
+      <c r="M34" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N34" s="52" t="s">
         <v>237</v>
       </c>
-      <c r="O34" s="43" t="s">
+      <c r="O34" s="52" t="s">
         <v>240</v>
       </c>
-      <c r="P34" s="43" t="s">
+      <c r="P34" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="Q34" s="43" t="s">
+      <c r="Q34" s="52" t="s">
         <v>246</v>
       </c>
-      <c r="R34" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="S34" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V34" s="55"/>
+      <c r="R34" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="S34" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V34" s="48"/>
     </row>
     <row r="35" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B35" s="10"/>
       <c r="C35" s="25"/>
-      <c r="D35" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F35" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G35" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H35" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="J35" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K35" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="L35" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="M35" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="N35" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="O35" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="P35" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q35" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="R35" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="S35" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V35" s="55"/>
+      <c r="D35" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J35" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="M35" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="N35" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="O35" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="P35" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q35" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="R35" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="S35" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V35" s="48"/>
     </row>
     <row r="36" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B36" s="14"/>
-      <c r="D36" s="43" t="s">
+      <c r="D36" s="52" t="s">
         <v>248</v>
       </c>
-      <c r="E36" s="43" t="s">
+      <c r="E36" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="F36" s="43" t="s">
+      <c r="F36" s="52" t="s">
         <v>248</v>
       </c>
-      <c r="G36" s="43" t="s">
+      <c r="G36" s="52" t="s">
         <v>338</v>
       </c>
-      <c r="H36" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" s="43" t="s">
+      <c r="H36" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="52" t="s">
         <v>248</v>
       </c>
-      <c r="J36" s="43" t="s">
+      <c r="J36" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="K36" s="43" t="s">
+      <c r="K36" s="52" t="s">
         <v>248</v>
       </c>
-      <c r="L36" s="43" t="s">
+      <c r="L36" s="52" t="s">
         <v>338</v>
       </c>
-      <c r="M36" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N36" s="43" t="s">
+      <c r="M36" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N36" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="O36" s="43" t="s">
+      <c r="O36" s="52" t="s">
         <v>218</v>
       </c>
-      <c r="P36" s="43" t="s">
+      <c r="P36" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="Q36" s="43" t="s">
+      <c r="Q36" s="52" t="s">
         <v>341</v>
       </c>
-      <c r="R36" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="S36" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V36" s="55"/>
+      <c r="R36" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="S36" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V36" s="48"/>
     </row>
     <row r="37" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B37" s="15">
         <f>B33+1</f>
         <v>9</v>
       </c>
-      <c r="D37" s="44" t="s">
+      <c r="D37" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="E37" s="44" t="s">
+      <c r="E37" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="F37" s="44" t="s">
+      <c r="F37" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="G37" s="44" t="s">
+      <c r="G37" s="50" t="s">
         <v>194</v>
       </c>
-      <c r="H37" s="44" t="s">
+      <c r="H37" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="I37" s="44" t="s">
+      <c r="I37" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="J37" s="44" t="s">
+      <c r="J37" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="K37" s="44" t="s">
+      <c r="K37" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="L37" s="44" t="s">
+      <c r="L37" s="50" t="s">
         <v>194</v>
       </c>
-      <c r="M37" s="44" t="s">
+      <c r="M37" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="N37" s="44" t="s">
+      <c r="N37" s="50" t="s">
         <v>196</v>
       </c>
-      <c r="O37" s="44" t="s">
+      <c r="O37" s="50" t="s">
         <v>198</v>
       </c>
-      <c r="P37" s="44" t="s">
+      <c r="P37" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="Q37" s="44" t="s">
+      <c r="Q37" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="R37" s="44" t="s">
+      <c r="R37" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="S37" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V37" s="55"/>
+      <c r="S37" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V37" s="48"/>
     </row>
     <row r="38" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="16"/>
-      <c r="D38" s="43" t="s">
+      <c r="D38" s="52" t="s">
         <v>249</v>
       </c>
-      <c r="E38" s="43" t="s">
+      <c r="E38" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="F38" s="43" t="s">
+      <c r="F38" s="52" t="s">
         <v>249</v>
       </c>
-      <c r="G38" s="43" t="s">
+      <c r="G38" s="52" t="s">
         <v>339</v>
       </c>
-      <c r="H38" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" s="43" t="s">
+      <c r="H38" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I38" s="52" t="s">
         <v>249</v>
       </c>
-      <c r="J38" s="43" t="s">
+      <c r="J38" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="K38" s="43" t="s">
+      <c r="K38" s="52" t="s">
         <v>249</v>
       </c>
-      <c r="L38" s="43" t="s">
+      <c r="L38" s="52" t="s">
         <v>339</v>
       </c>
-      <c r="M38" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N38" s="43" t="s">
+      <c r="M38" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N38" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="O38" s="43" t="s">
+      <c r="O38" s="52" t="s">
         <v>219</v>
       </c>
-      <c r="P38" s="43" t="s">
+      <c r="P38" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="Q38" s="43" t="s">
+      <c r="Q38" s="52" t="s">
         <v>342</v>
       </c>
-      <c r="R38" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="S38" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V38" s="55"/>
+      <c r="R38" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="S38" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V38" s="48"/>
     </row>
     <row r="39" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B39" s="10"/>
       <c r="C39" s="25"/>
-      <c r="D39" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="E39" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F39" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H39" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="J39" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K39" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="L39" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="M39" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="N39" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="O39" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="P39" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q39" s="41" t="s">
+      <c r="D39" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J39" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="K39" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="L39" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="M39" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="N39" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="O39" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="P39" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q39" s="51" t="s">
         <v>32</v>
       </c>
       <c r="R39" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S39" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V39" s="55"/>
+      <c r="S39" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V39" s="48"/>
     </row>
     <row r="40" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="14"/>
-      <c r="D40" s="43" t="s">
+      <c r="D40" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="E40" s="43" t="s">
+      <c r="E40" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="F40" s="43" t="s">
+      <c r="F40" s="52" t="s">
         <v>323</v>
       </c>
-      <c r="G40" s="43" t="s">
+      <c r="G40" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="H40" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" s="43" t="s">
+      <c r="H40" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="J40" s="43" t="s">
+      <c r="J40" s="52" t="s">
         <v>88</v>
       </c>
-      <c r="K40" s="43" t="s">
+      <c r="K40" s="52" t="s">
         <v>218</v>
       </c>
-      <c r="L40" s="43" t="s">
+      <c r="L40" s="52" t="s">
         <v>242</v>
       </c>
-      <c r="M40" s="43" t="s">
+      <c r="M40" s="52" t="s">
         <v>245</v>
       </c>
-      <c r="N40" s="43" t="s">
+      <c r="N40" s="52" t="s">
         <v>233</v>
       </c>
-      <c r="O40" s="43" t="s">
+      <c r="O40" s="52" t="s">
         <v>348</v>
       </c>
-      <c r="P40" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q40" s="43" t="s">
+      <c r="P40" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q40" s="52" t="s">
         <v>32</v>
       </c>
       <c r="R40" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S40" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V40" s="55"/>
+      <c r="S40" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V40" s="48"/>
     </row>
     <row r="41" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B41" s="15">
         <f>B37+1</f>
         <v>10</v>
       </c>
-      <c r="D41" s="44" t="s">
+      <c r="D41" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="E41" s="44" t="s">
+      <c r="E41" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="F41" s="44" t="s">
+      <c r="F41" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="G41" s="44" t="s">
+      <c r="G41" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="H41" s="44" t="s">
+      <c r="H41" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="I41" s="44" t="s">
+      <c r="I41" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="J41" s="44" t="s">
+      <c r="J41" s="50" t="s">
         <v>186</v>
       </c>
-      <c r="K41" s="44" t="s">
+      <c r="K41" s="50" t="s">
         <v>198</v>
       </c>
-      <c r="L41" s="44" t="s">
+      <c r="L41" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="M41" s="44" t="s">
+      <c r="M41" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="N41" s="44" t="s">
+      <c r="N41" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="O41" s="44" t="s">
+      <c r="O41" s="50" t="s">
         <v>202</v>
       </c>
-      <c r="P41" s="44" t="s">
+      <c r="P41" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="Q41" s="44" t="str">
+      <c r="Q41" s="50" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -5560,67 +5577,67 @@
       <c r="R41" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S41" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V41" s="55"/>
+      <c r="S41" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V41" s="48"/>
     </row>
     <row r="42" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="16"/>
-      <c r="D42" s="43" t="s">
+      <c r="D42" s="52" t="s">
         <v>237</v>
       </c>
-      <c r="E42" s="43" t="s">
+      <c r="E42" s="52" t="s">
         <v>240</v>
       </c>
-      <c r="F42" s="43" t="s">
+      <c r="F42" s="52" t="s">
         <v>324</v>
       </c>
-      <c r="G42" s="43" t="s">
+      <c r="G42" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="H42" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I42" s="43" t="s">
+      <c r="H42" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="J42" s="43" t="s">
+      <c r="J42" s="52" t="s">
         <v>89</v>
       </c>
-      <c r="K42" s="43" t="s">
+      <c r="K42" s="52" t="s">
         <v>219</v>
       </c>
-      <c r="L42" s="43" t="s">
+      <c r="L42" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="M42" s="43" t="s">
+      <c r="M42" s="52" t="s">
         <v>246</v>
       </c>
-      <c r="N42" s="43" t="s">
+      <c r="N42" s="52" t="s">
         <v>234</v>
       </c>
-      <c r="O42" s="43" t="s">
+      <c r="O42" s="52" t="s">
         <v>349</v>
       </c>
-      <c r="P42" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q42" s="43" t="s">
+      <c r="P42" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q42" s="52" t="s">
         <v>32</v>
       </c>
       <c r="R42" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S42" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V42" s="55"/>
+      <c r="S42" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V42" s="48"/>
     </row>
     <row r="43" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B43" s="10"/>
       <c r="C43" s="25"/>
-      <c r="D43" s="41" t="s">
+      <c r="D43" s="51" t="s">
         <v>32</v>
       </c>
       <c r="E43" s="41" t="s">
@@ -5665,14 +5682,14 @@
       <c r="R43" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S43" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V43" s="55"/>
+      <c r="S43" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V43" s="48"/>
     </row>
     <row r="44" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="14"/>
-      <c r="D44" s="43" t="s">
+      <c r="D44" s="52" t="s">
         <v>32</v>
       </c>
       <c r="E44" s="43" t="s">
@@ -5717,17 +5734,17 @@
       <c r="R44" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S44" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V44" s="55"/>
+      <c r="S44" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V44" s="48"/>
     </row>
     <row r="45" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B45" s="15">
         <f>B41+1</f>
         <v>11</v>
       </c>
-      <c r="D45" s="44" t="s">
+      <c r="D45" s="50" t="s">
         <v>38</v>
       </c>
       <c r="E45" s="44" t="s">
@@ -5772,14 +5789,14 @@
       <c r="R45" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S45" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V45" s="55"/>
+      <c r="S45" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V45" s="48"/>
     </row>
     <row r="46" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="16"/>
-      <c r="D46" s="43" t="s">
+      <c r="D46" s="52" t="s">
         <v>32</v>
       </c>
       <c r="E46" s="43" t="s">
@@ -5824,10 +5841,10 @@
       <c r="R46" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S46" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V46" s="55"/>
+      <c r="S46" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V46" s="48"/>
     </row>
     <row r="47" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B47" s="10"/>
@@ -5877,10 +5894,10 @@
       <c r="R47" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S47" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V47" s="55"/>
+      <c r="S47" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V47" s="48"/>
     </row>
     <row r="48" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B48" s="14"/>
@@ -5929,10 +5946,10 @@
       <c r="R48" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S48" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V48" s="55"/>
+      <c r="S48" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V48" s="48"/>
     </row>
     <row r="49" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B49" s="15">
@@ -5984,10 +6001,10 @@
       <c r="R49" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S49" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V49" s="55"/>
+      <c r="S49" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V49" s="48"/>
     </row>
     <row r="50" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="16"/>
@@ -6036,10 +6053,10 @@
       <c r="R50" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S50" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V50" s="55"/>
+      <c r="S50" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V50" s="48"/>
     </row>
     <row r="51" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B51" s="10"/>
@@ -6089,10 +6106,10 @@
       <c r="R51" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S51" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="V51" s="55"/>
+      <c r="S51" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V51" s="48"/>
     </row>
     <row r="52" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="14"/>
@@ -6141,10 +6158,10 @@
       <c r="R52" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S52" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V52" s="55"/>
+      <c r="S52" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V52" s="48"/>
     </row>
     <row r="53" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B53" s="15">
@@ -6196,10 +6213,10 @@
       <c r="R53" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S53" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V53" s="55"/>
+      <c r="S53" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V53" s="48"/>
     </row>
     <row r="54" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="16"/>
@@ -6248,10 +6265,10 @@
       <c r="R54" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S54" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V54" s="55"/>
+      <c r="S54" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V54" s="48"/>
     </row>
     <row r="55" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B55" s="10"/>
@@ -6301,10 +6318,10 @@
       <c r="R55" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S55" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V55" s="55"/>
+      <c r="S55" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V55" s="48"/>
     </row>
     <row r="56" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B56" s="14"/>
@@ -6353,10 +6370,10 @@
       <c r="R56" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S56" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V56" s="55"/>
+      <c r="S56" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V56" s="48"/>
     </row>
     <row r="57" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B57" s="15">
@@ -6408,10 +6425,10 @@
       <c r="R57" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S57" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V57" s="55"/>
+      <c r="S57" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V57" s="48"/>
     </row>
     <row r="58" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B58" s="16"/>
@@ -6460,10 +6477,10 @@
       <c r="R58" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S58" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V58" s="55"/>
+      <c r="S58" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V58" s="48"/>
     </row>
     <row r="59" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B59" s="10"/>
@@ -6513,10 +6530,10 @@
       <c r="R59" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S59" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V59" s="55"/>
+      <c r="S59" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V59" s="48"/>
     </row>
     <row r="60" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B60" s="14"/>
@@ -6565,10 +6582,10 @@
       <c r="R60" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S60" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V60" s="55"/>
+      <c r="S60" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V60" s="48"/>
     </row>
     <row r="61" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B61" s="15">
@@ -6620,10 +6637,10 @@
       <c r="R61" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S61" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V61" s="55"/>
+      <c r="S61" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V61" s="48"/>
     </row>
     <row r="62" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="16"/>
@@ -6672,10 +6689,10 @@
       <c r="R62" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S62" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V62" s="55"/>
+      <c r="S62" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V62" s="48"/>
     </row>
     <row r="63" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B63" s="10"/>
@@ -6725,10 +6742,10 @@
       <c r="R63" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S63" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V63" s="55"/>
+      <c r="S63" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V63" s="48"/>
     </row>
     <row r="64" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B64" s="14"/>
@@ -6777,10 +6794,10 @@
       <c r="R64" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S64" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V64" s="55"/>
+      <c r="S64" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V64" s="48"/>
     </row>
     <row r="65" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B65" s="15">
@@ -6832,10 +6849,10 @@
       <c r="R65" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S65" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V65" s="55"/>
+      <c r="S65" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V65" s="48"/>
     </row>
     <row r="66" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B66" s="16"/>
@@ -6884,10 +6901,10 @@
       <c r="R66" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S66" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V66" s="55"/>
+      <c r="S66" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V66" s="48"/>
     </row>
     <row r="67" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B67" s="10"/>
@@ -6937,10 +6954,10 @@
       <c r="R67" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S67" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V67" s="55"/>
+      <c r="S67" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V67" s="48"/>
     </row>
     <row r="68" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B68" s="14"/>
@@ -6989,10 +7006,10 @@
       <c r="R68" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S68" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V68" s="55"/>
+      <c r="S68" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V68" s="48"/>
     </row>
     <row r="69" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B69" s="15">
@@ -7044,10 +7061,10 @@
       <c r="R69" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S69" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V69" s="55"/>
+      <c r="S69" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V69" s="48"/>
     </row>
     <row r="70" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="16"/>
@@ -7096,10 +7113,10 @@
       <c r="R70" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S70" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V70" s="55"/>
+      <c r="S70" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V70" s="48"/>
     </row>
     <row r="71" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B71" s="10"/>
@@ -7149,10 +7166,10 @@
       <c r="R71" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S71" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V71" s="55"/>
+      <c r="S71" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V71" s="48"/>
     </row>
     <row r="72" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B72" s="14"/>
@@ -7201,10 +7218,10 @@
       <c r="R72" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S72" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V72" s="55"/>
+      <c r="S72" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V72" s="48"/>
     </row>
     <row r="73" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B73" s="15">
@@ -7256,10 +7273,10 @@
       <c r="R73" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S73" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V73" s="55"/>
+      <c r="S73" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V73" s="48"/>
     </row>
     <row r="74" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B74" s="16"/>
@@ -7308,10 +7325,10 @@
       <c r="R74" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S74" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V74" s="55"/>
+      <c r="S74" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V74" s="48"/>
     </row>
     <row r="75" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B75" s="10"/>
@@ -7361,10 +7378,10 @@
       <c r="R75" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S75" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V75" s="55"/>
+      <c r="S75" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V75" s="48"/>
     </row>
     <row r="76" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B76" s="14"/>
@@ -7413,10 +7430,10 @@
       <c r="R76" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S76" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V76" s="55"/>
+      <c r="S76" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V76" s="48"/>
     </row>
     <row r="77" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B77" s="15">
@@ -7468,10 +7485,10 @@
       <c r="R77" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S77" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V77" s="55"/>
+      <c r="S77" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V77" s="48"/>
     </row>
     <row r="78" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="16"/>
@@ -7520,10 +7537,10 @@
       <c r="R78" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S78" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V78" s="55"/>
+      <c r="S78" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V78" s="48"/>
     </row>
     <row r="79" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B79" s="10"/>
@@ -7573,10 +7590,10 @@
       <c r="R79" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S79" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="V79" s="55"/>
+      <c r="S79" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="V79" s="48"/>
     </row>
     <row r="80" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B80" s="14"/>
@@ -7625,10 +7642,10 @@
       <c r="R80" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S80" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="V80" s="55"/>
+      <c r="S80" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="V80" s="48"/>
     </row>
     <row r="81" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B81" s="15">
@@ -7680,10 +7697,10 @@
       <c r="R81" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S81" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="V81" s="55"/>
+      <c r="S81" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="V81" s="48"/>
     </row>
     <row r="82" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B82" s="16"/>
@@ -7732,10 +7749,10 @@
       <c r="R82" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S82" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="V82" s="56"/>
+      <c r="S82" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="V82" s="49"/>
     </row>
     <row r="83" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B83" s="10"/>
@@ -7785,7 +7802,7 @@
       <c r="R83" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S83" s="51" t="s">
+      <c r="S83" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V83" s="27"/>
@@ -7837,7 +7854,7 @@
       <c r="R84" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S84" s="46" t="s">
+      <c r="S84" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V84" s="7"/>
@@ -7892,7 +7909,7 @@
       <c r="R85" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S85" s="47" t="s">
+      <c r="S85" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V85" s="7"/>
@@ -7944,7 +7961,7 @@
       <c r="R86" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S86" s="49" t="s">
+      <c r="S86" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V86" s="7"/>
@@ -7997,7 +8014,7 @@
       <c r="R87" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S87" s="51" t="s">
+      <c r="S87" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V87" s="27"/>
@@ -8049,7 +8066,7 @@
       <c r="R88" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S88" s="46" t="s">
+      <c r="S88" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V88" s="7"/>
@@ -8104,7 +8121,7 @@
       <c r="R89" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S89" s="47" t="s">
+      <c r="S89" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V89" s="7"/>
@@ -8156,7 +8173,7 @@
       <c r="R90" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S90" s="49" t="s">
+      <c r="S90" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V90" s="7"/>
@@ -8209,7 +8226,7 @@
       <c r="R91" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S91" s="51" t="s">
+      <c r="S91" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V91" s="27"/>
@@ -8261,7 +8278,7 @@
       <c r="R92" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S92" s="46" t="s">
+      <c r="S92" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V92" s="7"/>
@@ -8316,7 +8333,7 @@
       <c r="R93" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S93" s="47" t="s">
+      <c r="S93" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V93" s="7"/>
@@ -8368,7 +8385,7 @@
       <c r="R94" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S94" s="49" t="s">
+      <c r="S94" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V94" s="7"/>
@@ -8421,7 +8438,7 @@
       <c r="R95" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S95" s="51" t="s">
+      <c r="S95" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V95" s="27"/>
@@ -8473,7 +8490,7 @@
       <c r="R96" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S96" s="46" t="s">
+      <c r="S96" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V96" s="7"/>
@@ -8528,7 +8545,7 @@
       <c r="R97" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S97" s="47" t="s">
+      <c r="S97" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V97" s="7"/>
@@ -8580,7 +8597,7 @@
       <c r="R98" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S98" s="49" t="s">
+      <c r="S98" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V98" s="7"/>
@@ -8633,7 +8650,7 @@
       <c r="R99" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S99" s="51" t="s">
+      <c r="S99" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V99" s="27"/>
@@ -8685,7 +8702,7 @@
       <c r="R100" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S100" s="46" t="s">
+      <c r="S100" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V100" s="7"/>
@@ -8740,7 +8757,7 @@
       <c r="R101" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S101" s="47" t="s">
+      <c r="S101" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V101" s="7"/>
@@ -8792,7 +8809,7 @@
       <c r="R102" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S102" s="49" t="s">
+      <c r="S102" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V102" s="7"/>
@@ -8845,7 +8862,7 @@
       <c r="R103" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S103" s="51" t="s">
+      <c r="S103" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V103" s="27"/>
@@ -8897,7 +8914,7 @@
       <c r="R104" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S104" s="46" t="s">
+      <c r="S104" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V104" s="7"/>
@@ -8952,7 +8969,7 @@
       <c r="R105" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S105" s="47" t="s">
+      <c r="S105" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V105" s="7"/>
@@ -9004,7 +9021,7 @@
       <c r="R106" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S106" s="49" t="s">
+      <c r="S106" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V106" s="7"/>
@@ -9057,7 +9074,7 @@
       <c r="R107" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S107" s="51" t="s">
+      <c r="S107" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V107" s="27"/>
@@ -9109,7 +9126,7 @@
       <c r="R108" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S108" s="46" t="s">
+      <c r="S108" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V108" s="7"/>
@@ -9164,7 +9181,7 @@
       <c r="R109" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S109" s="47" t="s">
+      <c r="S109" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V109" s="7"/>
@@ -9216,7 +9233,7 @@
       <c r="R110" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S110" s="49" t="s">
+      <c r="S110" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V110" s="7"/>
@@ -9269,7 +9286,7 @@
       <c r="R111" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S111" s="51" t="s">
+      <c r="S111" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V111" s="27"/>
@@ -9321,7 +9338,7 @@
       <c r="R112" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S112" s="46" t="s">
+      <c r="S112" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V112" s="7"/>
@@ -9376,7 +9393,7 @@
       <c r="R113" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S113" s="47" t="s">
+      <c r="S113" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V113" s="7"/>
@@ -9428,7 +9445,7 @@
       <c r="R114" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S114" s="49" t="s">
+      <c r="S114" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V114" s="7"/>
@@ -9481,10 +9498,10 @@
       <c r="R115" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S115" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="U115" s="51"/>
+      <c r="S115" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="U115" s="45"/>
       <c r="V115" s="27"/>
     </row>
     <row r="116" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
@@ -9534,7 +9551,7 @@
       <c r="R116" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S116" s="46" t="s">
+      <c r="S116" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V116" s="7"/>
@@ -9544,7 +9561,7 @@
         <f>B113+1</f>
         <v>29</v>
       </c>
-      <c r="D117" s="53" t="s">
+      <c r="D117" s="46" t="s">
         <v>32</v>
       </c>
       <c r="E117" s="44" t="s">
@@ -9589,7 +9606,7 @@
       <c r="R117" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S117" s="47" t="s">
+      <c r="S117" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V117" s="7"/>
@@ -9641,7 +9658,7 @@
       <c r="R118" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S118" s="49" t="s">
+      <c r="S118" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V118" s="7"/>
@@ -9694,7 +9711,7 @@
       <c r="R119" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S119" s="51" t="s">
+      <c r="S119" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V119" s="27"/>
@@ -9746,7 +9763,7 @@
       <c r="R120" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S120" s="46" t="s">
+      <c r="S120" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V120" s="7"/>
@@ -9801,7 +9818,7 @@
       <c r="R121" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S121" s="47" t="s">
+      <c r="S121" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V121" s="7"/>
@@ -9853,7 +9870,7 @@
       <c r="R122" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S122" s="49" t="s">
+      <c r="S122" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V122" s="7"/>
@@ -9906,7 +9923,7 @@
       <c r="R123" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S123" s="51" t="s">
+      <c r="S123" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V123" s="27"/>
@@ -9958,7 +9975,7 @@
       <c r="R124" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S124" s="46" t="s">
+      <c r="S124" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V124" s="7"/>
@@ -9983,7 +10000,7 @@
       <c r="H125" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="I125" s="53" t="s">
+      <c r="I125" s="46" t="s">
         <v>32</v>
       </c>
       <c r="J125" s="44" t="s">
@@ -10013,7 +10030,7 @@
       <c r="R125" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S125" s="47" t="s">
+      <c r="S125" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V125" s="7"/>
@@ -10065,7 +10082,7 @@
       <c r="R126" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S126" s="49" t="s">
+      <c r="S126" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V126" s="7"/>
@@ -10118,7 +10135,7 @@
       <c r="R127" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S127" s="51" t="s">
+      <c r="S127" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V127" s="27"/>
@@ -10170,7 +10187,7 @@
       <c r="R128" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S128" s="46" t="s">
+      <c r="S128" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V128" s="7"/>
@@ -10210,7 +10227,7 @@
       <c r="M129" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="N129" s="53" t="s">
+      <c r="N129" s="46" t="s">
         <v>32</v>
       </c>
       <c r="O129" s="44" t="s">
@@ -10225,7 +10242,7 @@
       <c r="R129" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S129" s="47" t="s">
+      <c r="S129" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V129" s="7"/>
@@ -10277,7 +10294,7 @@
       <c r="R130" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S130" s="49" t="s">
+      <c r="S130" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V130" s="7"/>
@@ -10330,7 +10347,7 @@
       <c r="R131" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S131" s="51" t="s">
+      <c r="S131" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V131" s="27"/>
@@ -10382,7 +10399,7 @@
       <c r="R132" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S132" s="46" t="s">
+      <c r="S132" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V132" s="7"/>
@@ -10437,7 +10454,7 @@
       <c r="R133" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S133" s="47" t="s">
+      <c r="S133" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V133" s="7"/>
@@ -10489,7 +10506,7 @@
       <c r="R134" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S134" s="49" t="s">
+      <c r="S134" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V134" s="7"/>
@@ -10542,7 +10559,7 @@
       <c r="R135" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S135" s="51" t="s">
+      <c r="S135" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V135" s="27"/>
@@ -10594,7 +10611,7 @@
       <c r="R136" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S136" s="46" t="s">
+      <c r="S136" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V136" s="7"/>
@@ -10649,7 +10666,7 @@
       <c r="R137" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S137" s="47" t="s">
+      <c r="S137" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V137" s="7"/>
@@ -10701,7 +10718,7 @@
       <c r="R138" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S138" s="49" t="s">
+      <c r="S138" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V138" s="7"/>
@@ -10754,7 +10771,7 @@
       <c r="R139" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S139" s="51" t="s">
+      <c r="S139" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V139" s="27"/>
@@ -10806,7 +10823,7 @@
       <c r="R140" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S140" s="46" t="s">
+      <c r="S140" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V140" s="7"/>
@@ -10861,7 +10878,7 @@
       <c r="R141" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S141" s="47" t="s">
+      <c r="S141" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V141" s="7"/>
@@ -10913,7 +10930,7 @@
       <c r="R142" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S142" s="49" t="s">
+      <c r="S142" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V142" s="7"/>
@@ -10966,7 +10983,7 @@
       <c r="R143" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S143" s="51" t="s">
+      <c r="S143" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V143" s="27"/>
@@ -11018,7 +11035,7 @@
       <c r="R144" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S144" s="46" t="s">
+      <c r="S144" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V144" s="7"/>
@@ -11073,7 +11090,7 @@
       <c r="R145" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S145" s="47" t="s">
+      <c r="S145" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V145" s="7"/>
@@ -11125,7 +11142,7 @@
       <c r="R146" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S146" s="49" t="s">
+      <c r="S146" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V146" s="7"/>
@@ -11178,7 +11195,7 @@
       <c r="R147" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S147" s="51" t="s">
+      <c r="S147" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V147" s="27"/>
@@ -11230,7 +11247,7 @@
       <c r="R148" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S148" s="46" t="s">
+      <c r="S148" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V148" s="7"/>
@@ -11279,13 +11296,13 @@
       <c r="P149" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="Q149" s="53" t="s">
+      <c r="Q149" s="46" t="s">
         <v>32</v>
       </c>
       <c r="R149" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S149" s="47" t="s">
+      <c r="S149" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V149" s="7"/>
@@ -11337,7 +11354,7 @@
       <c r="R150" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S150" s="49" t="s">
+      <c r="S150" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V150" s="7"/>
@@ -11390,7 +11407,7 @@
       <c r="R151" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S151" s="51" t="s">
+      <c r="S151" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V151" s="27"/>
@@ -11442,7 +11459,7 @@
       <c r="R152" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S152" s="46" t="s">
+      <c r="S152" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V152" s="7"/>
@@ -11479,7 +11496,7 @@
       <c r="L153" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="M153" s="53" t="s">
+      <c r="M153" s="46" t="s">
         <v>32</v>
       </c>
       <c r="N153" s="44" t="s">
@@ -11497,7 +11514,7 @@
       <c r="R153" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S153" s="47" t="s">
+      <c r="S153" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V153" s="7"/>
@@ -11549,7 +11566,7 @@
       <c r="R154" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S154" s="49" t="s">
+      <c r="S154" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V154" s="7"/>
@@ -11602,7 +11619,7 @@
       <c r="R155" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S155" s="51" t="s">
+      <c r="S155" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V155" s="27"/>
@@ -11654,7 +11671,7 @@
       <c r="R156" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S156" s="46" t="s">
+      <c r="S156" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V156" s="7"/>
@@ -11709,7 +11726,7 @@
       <c r="R157" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S157" s="47" t="s">
+      <c r="S157" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V157" s="7"/>
@@ -11761,7 +11778,7 @@
       <c r="R158" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S158" s="49" t="s">
+      <c r="S158" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V158" s="7"/>
@@ -11814,7 +11831,7 @@
       <c r="R159" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S159" s="51" t="s">
+      <c r="S159" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V159" s="27"/>
@@ -11866,7 +11883,7 @@
       <c r="R160" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S160" s="46" t="s">
+      <c r="S160" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V160" s="7"/>
@@ -11921,7 +11938,7 @@
       <c r="R161" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S161" s="47" t="s">
+      <c r="S161" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V161" s="7"/>
@@ -11973,7 +11990,7 @@
       <c r="R162" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S162" s="49" t="s">
+      <c r="S162" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V162" s="7"/>
@@ -12026,7 +12043,7 @@
       <c r="R163" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S163" s="26" t="s">
+      <c r="S163" s="61" t="s">
         <v>32</v>
       </c>
       <c r="V163" s="27"/>
@@ -12078,7 +12095,7 @@
       <c r="R164" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S164" s="46" t="s">
+      <c r="S164" s="56" t="s">
         <v>32</v>
       </c>
       <c r="V164" s="7"/>
@@ -12133,7 +12150,7 @@
       <c r="R165" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S165" s="47" t="s">
+      <c r="S165" s="57" t="s">
         <v>32</v>
       </c>
       <c r="V165" s="7"/>
@@ -12185,7 +12202,7 @@
       <c r="R166" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S166" s="49" t="s">
+      <c r="S166" s="60" t="s">
         <v>32</v>
       </c>
       <c r="V166" s="7"/>
@@ -12238,7 +12255,7 @@
       <c r="R167" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S167" s="6" t="s">
+      <c r="S167" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -12290,7 +12307,7 @@
       <c r="R168" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S168" s="6" t="s">
+      <c r="S168" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -12345,7 +12362,7 @@
       <c r="R169" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S169" s="6" t="s">
+      <c r="S169" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -12397,7 +12414,7 @@
       <c r="R170" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S170" s="6" t="s">
+      <c r="S170" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -12449,7 +12466,7 @@
       <c r="R171" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S171" s="6" t="s">
+      <c r="S171" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -12501,7 +12518,7 @@
       <c r="R172" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S172" s="6" t="s">
+      <c r="S172" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -12556,7 +12573,7 @@
       <c r="R173" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S173" s="6" t="s">
+      <c r="S173" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -12608,7 +12625,7 @@
       <c r="R174" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S174" s="6" t="s">
+      <c r="S174" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -12660,7 +12677,7 @@
       <c r="R175" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S175" s="6" t="s">
+      <c r="S175" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -12712,7 +12729,7 @@
       <c r="R176" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S176" s="6" t="s">
+      <c r="S176" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -12767,7 +12784,7 @@
       <c r="R177" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S177" s="6" t="s">
+      <c r="S177" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -12819,7 +12836,7 @@
       <c r="R178" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S178" s="6" t="s">
+      <c r="S178" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -12871,7 +12888,7 @@
       <c r="R179" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S179" s="6" t="s">
+      <c r="S179" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -12923,7 +12940,7 @@
       <c r="R180" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S180" s="6" t="s">
+      <c r="S180" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -12978,7 +12995,7 @@
       <c r="R181" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S181" s="6" t="s">
+      <c r="S181" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13030,7 +13047,7 @@
       <c r="R182" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S182" s="6" t="s">
+      <c r="S182" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13082,7 +13099,7 @@
       <c r="R183" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S183" s="6" t="s">
+      <c r="S183" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13134,7 +13151,7 @@
       <c r="R184" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S184" s="6" t="s">
+      <c r="S184" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13189,7 +13206,7 @@
       <c r="R185" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S185" s="6" t="s">
+      <c r="S185" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13241,7 +13258,7 @@
       <c r="R186" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S186" s="6" t="s">
+      <c r="S186" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13293,7 +13310,7 @@
       <c r="R187" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S187" s="6" t="s">
+      <c r="S187" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13345,7 +13362,7 @@
       <c r="R188" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S188" s="6" t="s">
+      <c r="S188" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13400,7 +13417,7 @@
       <c r="R189" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S189" s="6" t="s">
+      <c r="S189" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13452,7 +13469,7 @@
       <c r="R190" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S190" s="6" t="s">
+      <c r="S190" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13504,7 +13521,7 @@
       <c r="R191" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S191" s="6" t="s">
+      <c r="S191" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13556,7 +13573,7 @@
       <c r="R192" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S192" s="6" t="s">
+      <c r="S192" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13611,7 +13628,7 @@
       <c r="R193" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S193" s="6" t="s">
+      <c r="S193" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13663,7 +13680,7 @@
       <c r="R194" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S194" s="6" t="s">
+      <c r="S194" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13715,7 +13732,7 @@
       <c r="R195" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S195" s="6" t="s">
+      <c r="S195" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13767,7 +13784,7 @@
       <c r="R196" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S196" s="6" t="s">
+      <c r="S196" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13822,7 +13839,7 @@
       <c r="R197" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S197" s="6" t="s">
+      <c r="S197" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13874,7 +13891,7 @@
       <c r="R198" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S198" s="6" t="s">
+      <c r="S198" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13926,7 +13943,7 @@
       <c r="R199" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S199" s="6" t="s">
+      <c r="S199" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -13978,7 +13995,7 @@
       <c r="R200" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S200" s="6" t="s">
+      <c r="S200" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14033,7 +14050,7 @@
       <c r="R201" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S201" s="6" t="s">
+      <c r="S201" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14085,7 +14102,7 @@
       <c r="R202" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S202" s="6" t="s">
+      <c r="S202" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14137,7 +14154,7 @@
       <c r="R203" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S203" s="6" t="s">
+      <c r="S203" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14189,7 +14206,7 @@
       <c r="R204" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S204" s="6" t="s">
+      <c r="S204" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14244,7 +14261,7 @@
       <c r="R205" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S205" s="6" t="s">
+      <c r="S205" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14296,7 +14313,7 @@
       <c r="R206" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S206" s="6" t="s">
+      <c r="S206" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14348,7 +14365,7 @@
       <c r="R207" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S207" s="6" t="s">
+      <c r="S207" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14400,7 +14417,7 @@
       <c r="R208" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S208" s="6" t="s">
+      <c r="S208" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14455,7 +14472,7 @@
       <c r="R209" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S209" s="6" t="s">
+      <c r="S209" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14507,7 +14524,7 @@
       <c r="R210" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S210" s="6" t="s">
+      <c r="S210" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14559,7 +14576,7 @@
       <c r="R211" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S211" s="6" t="s">
+      <c r="S211" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14611,7 +14628,7 @@
       <c r="R212" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S212" s="6" t="s">
+      <c r="S212" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14666,7 +14683,7 @@
       <c r="R213" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S213" s="6" t="s">
+      <c r="S213" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14718,7 +14735,7 @@
       <c r="R214" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S214" s="6" t="s">
+      <c r="S214" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14770,7 +14787,7 @@
       <c r="R215" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S215" s="6" t="s">
+      <c r="S215" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14822,7 +14839,7 @@
       <c r="R216" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S216" s="6" t="s">
+      <c r="S216" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14877,7 +14894,7 @@
       <c r="R217" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S217" s="6" t="s">
+      <c r="S217" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14929,7 +14946,7 @@
       <c r="R218" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S218" s="6" t="s">
+      <c r="S218" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14981,7 +14998,7 @@
       <c r="R219" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S219" s="6" t="s">
+      <c r="S219" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15033,7 +15050,7 @@
       <c r="R220" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S220" s="6" t="s">
+      <c r="S220" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15088,7 +15105,7 @@
       <c r="R221" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S221" s="6" t="s">
+      <c r="S221" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15140,7 +15157,7 @@
       <c r="R222" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S222" s="6" t="s">
+      <c r="S222" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15192,7 +15209,7 @@
       <c r="R223" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S223" s="6" t="s">
+      <c r="S223" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15244,7 +15261,7 @@
       <c r="R224" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S224" s="6" t="s">
+      <c r="S224" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15299,7 +15316,7 @@
       <c r="R225" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S225" s="6" t="s">
+      <c r="S225" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15351,7 +15368,7 @@
       <c r="R226" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S226" s="6" t="s">
+      <c r="S226" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15403,7 +15420,7 @@
       <c r="R227" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S227" s="6" t="s">
+      <c r="S227" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15455,7 +15472,7 @@
       <c r="R228" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S228" s="6" t="s">
+      <c r="S228" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15510,7 +15527,7 @@
       <c r="R229" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S229" s="6" t="s">
+      <c r="S229" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15562,7 +15579,7 @@
       <c r="R230" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S230" s="6" t="s">
+      <c r="S230" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15614,7 +15631,7 @@
       <c r="R231" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S231" s="6" t="s">
+      <c r="S231" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15666,7 +15683,7 @@
       <c r="R232" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S232" s="6" t="s">
+      <c r="S232" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15721,7 +15738,7 @@
       <c r="R233" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S233" s="6" t="s">
+      <c r="S233" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15773,7 +15790,7 @@
       <c r="R234" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S234" s="6" t="s">
+      <c r="S234" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15825,7 +15842,7 @@
       <c r="R235" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S235" s="6" t="s">
+      <c r="S235" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15877,7 +15894,7 @@
       <c r="R236" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S236" s="6" t="s">
+      <c r="S236" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15932,7 +15949,7 @@
       <c r="R237" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S237" s="6" t="s">
+      <c r="S237" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -15984,7 +16001,7 @@
       <c r="R238" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S238" s="6" t="s">
+      <c r="S238" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16036,7 +16053,7 @@
       <c r="R239" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S239" s="6" t="s">
+      <c r="S239" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16088,7 +16105,7 @@
       <c r="R240" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S240" s="6" t="s">
+      <c r="S240" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16143,7 +16160,7 @@
       <c r="R241" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S241" s="6" t="s">
+      <c r="S241" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16195,7 +16212,7 @@
       <c r="R242" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S242" s="6" t="s">
+      <c r="S242" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16247,7 +16264,7 @@
       <c r="R243" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S243" s="6" t="s">
+      <c r="S243" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16299,7 +16316,7 @@
       <c r="R244" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S244" s="6" t="s">
+      <c r="S244" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16354,7 +16371,7 @@
       <c r="R245" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S245" s="6" t="s">
+      <c r="S245" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16406,7 +16423,7 @@
       <c r="R246" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S246" s="6" t="s">
+      <c r="S246" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16458,7 +16475,7 @@
       <c r="R247" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S247" s="6" t="s">
+      <c r="S247" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16510,7 +16527,7 @@
       <c r="R248" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S248" s="6" t="s">
+      <c r="S248" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16565,7 +16582,7 @@
       <c r="R249" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S249" s="6" t="s">
+      <c r="S249" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16617,7 +16634,7 @@
       <c r="R250" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S250" s="6" t="s">
+      <c r="S250" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16669,7 +16686,7 @@
       <c r="R251" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S251" s="6" t="s">
+      <c r="S251" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16721,7 +16738,7 @@
       <c r="R252" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S252" s="6" t="s">
+      <c r="S252" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16776,7 +16793,7 @@
       <c r="R253" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S253" s="6" t="s">
+      <c r="S253" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16828,7 +16845,7 @@
       <c r="R254" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S254" s="6" t="s">
+      <c r="S254" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16880,7 +16897,7 @@
       <c r="R255" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S255" s="6" t="s">
+      <c r="S255" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16932,7 +16949,7 @@
       <c r="R256" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S256" s="6" t="s">
+      <c r="S256" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -16987,7 +17004,7 @@
       <c r="R257" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S257" s="6" t="s">
+      <c r="S257" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17039,7 +17056,7 @@
       <c r="R258" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S258" s="6" t="s">
+      <c r="S258" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17091,7 +17108,7 @@
       <c r="R259" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S259" s="6" t="s">
+      <c r="S259" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17143,7 +17160,7 @@
       <c r="R260" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S260" s="6" t="s">
+      <c r="S260" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17198,7 +17215,7 @@
       <c r="R261" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S261" s="6" t="s">
+      <c r="S261" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17250,7 +17267,7 @@
       <c r="R262" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S262" s="6" t="s">
+      <c r="S262" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17302,7 +17319,7 @@
       <c r="R263" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S263" s="6" t="s">
+      <c r="S263" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17354,7 +17371,7 @@
       <c r="R264" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S264" s="6" t="s">
+      <c r="S264" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17409,7 +17426,7 @@
       <c r="R265" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S265" s="6" t="s">
+      <c r="S265" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17461,7 +17478,7 @@
       <c r="R266" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S266" s="6" t="s">
+      <c r="S266" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17513,7 +17530,7 @@
       <c r="R267" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S267" s="6" t="s">
+      <c r="S267" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17565,7 +17582,7 @@
       <c r="R268" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S268" s="6" t="s">
+      <c r="S268" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17620,7 +17637,7 @@
       <c r="R269" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S269" s="6" t="s">
+      <c r="S269" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17672,7 +17689,7 @@
       <c r="R270" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S270" s="6" t="s">
+      <c r="S270" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17724,7 +17741,7 @@
       <c r="R271" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S271" s="6" t="s">
+      <c r="S271" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17776,7 +17793,7 @@
       <c r="R272" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S272" s="6" t="s">
+      <c r="S272" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17831,7 +17848,7 @@
       <c r="R273" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S273" s="6" t="s">
+      <c r="S273" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17883,7 +17900,7 @@
       <c r="R274" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S274" s="6" t="s">
+      <c r="S274" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17935,7 +17952,7 @@
       <c r="R275" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S275" s="6" t="s">
+      <c r="S275" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -17987,7 +18004,7 @@
       <c r="R276" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S276" s="6" t="s">
+      <c r="S276" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18042,7 +18059,7 @@
       <c r="R277" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S277" s="6" t="s">
+      <c r="S277" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18094,7 +18111,7 @@
       <c r="R278" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S278" s="6" t="s">
+      <c r="S278" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18146,7 +18163,7 @@
       <c r="R279" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S279" s="6" t="s">
+      <c r="S279" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18198,7 +18215,7 @@
       <c r="R280" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S280" s="6" t="s">
+      <c r="S280" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18253,7 +18270,7 @@
       <c r="R281" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S281" s="6" t="s">
+      <c r="S281" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18305,7 +18322,7 @@
       <c r="R282" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S282" s="6" t="s">
+      <c r="S282" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18357,7 +18374,7 @@
       <c r="R283" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S283" s="6" t="s">
+      <c r="S283" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18409,7 +18426,7 @@
       <c r="R284" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S284" s="6" t="s">
+      <c r="S284" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18464,7 +18481,7 @@
       <c r="R285" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S285" s="6" t="s">
+      <c r="S285" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18516,7 +18533,7 @@
       <c r="R286" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S286" s="6" t="s">
+      <c r="S286" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18568,7 +18585,7 @@
       <c r="R287" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S287" s="6" t="s">
+      <c r="S287" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18620,7 +18637,7 @@
       <c r="R288" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S288" s="6" t="s">
+      <c r="S288" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18675,7 +18692,7 @@
       <c r="R289" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S289" s="6" t="s">
+      <c r="S289" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18727,7 +18744,7 @@
       <c r="R290" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S290" s="6" t="s">
+      <c r="S290" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18779,7 +18796,7 @@
       <c r="R291" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S291" s="6" t="s">
+      <c r="S291" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18831,7 +18848,7 @@
       <c r="R292" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S292" s="6" t="s">
+      <c r="S292" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18886,7 +18903,7 @@
       <c r="R293" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S293" s="6" t="s">
+      <c r="S293" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18938,7 +18955,7 @@
       <c r="R294" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S294" s="6" t="s">
+      <c r="S294" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18990,7 +19007,7 @@
       <c r="R295" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S295" s="6" t="s">
+      <c r="S295" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19042,7 +19059,7 @@
       <c r="R296" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S296" s="6" t="s">
+      <c r="S296" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19097,7 +19114,7 @@
       <c r="R297" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S297" s="6" t="s">
+      <c r="S297" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19149,7 +19166,7 @@
       <c r="R298" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S298" s="6" t="s">
+      <c r="S298" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19201,7 +19218,7 @@
       <c r="R299" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S299" s="6" t="s">
+      <c r="S299" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19253,7 +19270,7 @@
       <c r="R300" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S300" s="6" t="s">
+      <c r="S300" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19308,7 +19325,7 @@
       <c r="R301" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S301" s="6" t="s">
+      <c r="S301" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19360,7 +19377,7 @@
       <c r="R302" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S302" s="6" t="s">
+      <c r="S302" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19412,7 +19429,7 @@
       <c r="R303" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S303" s="6" t="s">
+      <c r="S303" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19464,7 +19481,7 @@
       <c r="R304" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S304" s="6" t="s">
+      <c r="S304" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19519,7 +19536,7 @@
       <c r="R305" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S305" s="6" t="s">
+      <c r="S305" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19571,7 +19588,7 @@
       <c r="R306" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S306" s="6" t="s">
+      <c r="S306" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19623,7 +19640,7 @@
       <c r="R307" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S307" s="6" t="s">
+      <c r="S307" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19675,7 +19692,7 @@
       <c r="R308" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S308" s="6" t="s">
+      <c r="S308" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19730,7 +19747,7 @@
       <c r="R309" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S309" s="6" t="s">
+      <c r="S309" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19782,7 +19799,7 @@
       <c r="R310" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S310" s="6" t="s">
+      <c r="S310" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19834,7 +19851,7 @@
       <c r="R311" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S311" s="6" t="s">
+      <c r="S311" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19886,7 +19903,7 @@
       <c r="R312" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S312" s="6" t="s">
+      <c r="S312" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19941,7 +19958,7 @@
       <c r="R313" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S313" s="6" t="s">
+      <c r="S313" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -19993,7 +20010,7 @@
       <c r="R314" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S314" s="6" t="s">
+      <c r="S314" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20045,7 +20062,7 @@
       <c r="R315" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S315" s="6" t="s">
+      <c r="S315" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20097,7 +20114,7 @@
       <c r="R316" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S316" s="6" t="s">
+      <c r="S316" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20152,7 +20169,7 @@
       <c r="R317" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S317" s="6" t="s">
+      <c r="S317" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20204,7 +20221,7 @@
       <c r="R318" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S318" s="6" t="s">
+      <c r="S318" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20256,7 +20273,7 @@
       <c r="R319" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S319" s="6" t="s">
+      <c r="S319" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20308,7 +20325,7 @@
       <c r="R320" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S320" s="6" t="s">
+      <c r="S320" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20363,7 +20380,7 @@
       <c r="R321" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S321" s="6" t="s">
+      <c r="S321" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20415,7 +20432,7 @@
       <c r="R322" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S322" s="6" t="s">
+      <c r="S322" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20467,7 +20484,7 @@
       <c r="R323" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S323" s="6" t="s">
+      <c r="S323" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20519,7 +20536,7 @@
       <c r="R324" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S324" s="6" t="s">
+      <c r="S324" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20574,7 +20591,7 @@
       <c r="R325" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S325" s="6" t="s">
+      <c r="S325" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20626,7 +20643,7 @@
       <c r="R326" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S326" s="6" t="s">
+      <c r="S326" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20678,7 +20695,7 @@
       <c r="R327" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S327" s="6" t="s">
+      <c r="S327" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20730,7 +20747,7 @@
       <c r="R328" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S328" s="6" t="s">
+      <c r="S328" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20785,7 +20802,7 @@
       <c r="R329" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S329" s="6" t="s">
+      <c r="S329" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20837,7 +20854,7 @@
       <c r="R330" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S330" s="6" t="s">
+      <c r="S330" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20889,7 +20906,7 @@
       <c r="R331" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S331" s="6" t="s">
+      <c r="S331" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20941,7 +20958,7 @@
       <c r="R332" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S332" s="6" t="s">
+      <c r="S332" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -20996,7 +21013,7 @@
       <c r="R333" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S333" s="6" t="s">
+      <c r="S333" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21048,7 +21065,7 @@
       <c r="R334" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S334" s="6" t="s">
+      <c r="S334" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21100,7 +21117,7 @@
       <c r="R335" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S335" s="6" t="s">
+      <c r="S335" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21152,7 +21169,7 @@
       <c r="R336" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S336" s="6" t="s">
+      <c r="S336" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21207,7 +21224,7 @@
       <c r="R337" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S337" s="6" t="s">
+      <c r="S337" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21259,7 +21276,7 @@
       <c r="R338" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S338" s="6" t="s">
+      <c r="S338" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21311,7 +21328,7 @@
       <c r="R339" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S339" s="6" t="s">
+      <c r="S339" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21363,7 +21380,7 @@
       <c r="R340" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S340" s="6" t="s">
+      <c r="S340" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21418,7 +21435,7 @@
       <c r="R341" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S341" s="6" t="s">
+      <c r="S341" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21470,7 +21487,7 @@
       <c r="R342" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S342" s="6" t="s">
+      <c r="S342" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21522,7 +21539,7 @@
       <c r="R343" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S343" s="6" t="s">
+      <c r="S343" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21574,7 +21591,7 @@
       <c r="R344" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S344" s="6" t="s">
+      <c r="S344" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21629,7 +21646,7 @@
       <c r="R345" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S345" s="6" t="s">
+      <c r="S345" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21681,7 +21698,7 @@
       <c r="R346" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S346" s="6" t="s">
+      <c r="S346" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21733,7 +21750,7 @@
       <c r="R347" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S347" s="6" t="s">
+      <c r="S347" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21785,7 +21802,7 @@
       <c r="R348" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S348" s="6" t="s">
+      <c r="S348" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21840,7 +21857,7 @@
       <c r="R349" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S349" s="6" t="s">
+      <c r="S349" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21892,7 +21909,7 @@
       <c r="R350" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S350" s="6" t="s">
+      <c r="S350" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21944,7 +21961,7 @@
       <c r="R351" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S351" s="6" t="s">
+      <c r="S351" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -21996,7 +22013,7 @@
       <c r="R352" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S352" s="6" t="s">
+      <c r="S352" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22051,7 +22068,7 @@
       <c r="R353" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S353" s="6" t="s">
+      <c r="S353" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22103,7 +22120,7 @@
       <c r="R354" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S354" s="6" t="s">
+      <c r="S354" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22155,7 +22172,7 @@
       <c r="R355" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S355" s="6" t="s">
+      <c r="S355" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22207,7 +22224,7 @@
       <c r="R356" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S356" s="6" t="s">
+      <c r="S356" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22262,7 +22279,7 @@
       <c r="R357" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S357" s="6" t="s">
+      <c r="S357" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22314,7 +22331,7 @@
       <c r="R358" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S358" s="6" t="s">
+      <c r="S358" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22366,7 +22383,7 @@
       <c r="R359" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S359" s="6" t="s">
+      <c r="S359" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22418,7 +22435,7 @@
       <c r="R360" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S360" s="6" t="s">
+      <c r="S360" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22473,7 +22490,7 @@
       <c r="R361" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S361" s="6" t="s">
+      <c r="S361" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22525,7 +22542,7 @@
       <c r="R362" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S362" s="6" t="s">
+      <c r="S362" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22577,7 +22594,7 @@
       <c r="R363" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S363" s="6" t="s">
+      <c r="S363" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22629,7 +22646,7 @@
       <c r="R364" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S364" s="6" t="s">
+      <c r="S364" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22684,7 +22701,7 @@
       <c r="R365" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S365" s="6" t="s">
+      <c r="S365" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22736,7 +22753,7 @@
       <c r="R366" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S366" s="6" t="s">
+      <c r="S366" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22788,7 +22805,7 @@
       <c r="R367" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S367" s="6" t="s">
+      <c r="S367" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22840,7 +22857,7 @@
       <c r="R368" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S368" s="6" t="s">
+      <c r="S368" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22895,7 +22912,7 @@
       <c r="R369" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S369" s="6" t="s">
+      <c r="S369" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22947,7 +22964,7 @@
       <c r="R370" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S370" s="6" t="s">
+      <c r="S370" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -22999,7 +23016,7 @@
       <c r="R371" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S371" s="6" t="s">
+      <c r="S371" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23051,7 +23068,7 @@
       <c r="R372" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S372" s="6" t="s">
+      <c r="S372" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23106,7 +23123,7 @@
       <c r="R373" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S373" s="6" t="s">
+      <c r="S373" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23158,7 +23175,7 @@
       <c r="R374" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S374" s="6" t="s">
+      <c r="S374" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23210,7 +23227,7 @@
       <c r="R375" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S375" s="6" t="s">
+      <c r="S375" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23262,7 +23279,7 @@
       <c r="R376" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S376" s="6" t="s">
+      <c r="S376" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23317,7 +23334,7 @@
       <c r="R377" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S377" s="6" t="s">
+      <c r="S377" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23369,7 +23386,7 @@
       <c r="R378" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S378" s="6" t="s">
+      <c r="S378" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23421,7 +23438,7 @@
       <c r="R379" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S379" s="6" t="s">
+      <c r="S379" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23473,7 +23490,7 @@
       <c r="R380" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S380" s="6" t="s">
+      <c r="S380" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23528,7 +23545,7 @@
       <c r="R381" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S381" s="6" t="s">
+      <c r="S381" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23580,7 +23597,7 @@
       <c r="R382" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S382" s="6" t="s">
+      <c r="S382" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23632,7 +23649,7 @@
       <c r="R383" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S383" s="6" t="s">
+      <c r="S383" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23684,7 +23701,7 @@
       <c r="R384" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S384" s="6" t="s">
+      <c r="S384" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23739,7 +23756,7 @@
       <c r="R385" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S385" s="6" t="s">
+      <c r="S385" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23791,7 +23808,7 @@
       <c r="R386" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S386" s="6" t="s">
+      <c r="S386" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23843,7 +23860,7 @@
       <c r="R387" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S387" s="6" t="s">
+      <c r="S387" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23895,7 +23912,7 @@
       <c r="R388" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S388" s="6" t="s">
+      <c r="S388" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -23950,7 +23967,7 @@
       <c r="R389" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S389" s="6" t="s">
+      <c r="S389" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24002,7 +24019,7 @@
       <c r="R390" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S390" s="6" t="s">
+      <c r="S390" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24054,7 +24071,7 @@
       <c r="R391" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S391" s="6" t="s">
+      <c r="S391" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24106,7 +24123,7 @@
       <c r="R392" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S392" s="6" t="s">
+      <c r="S392" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24161,7 +24178,7 @@
       <c r="R393" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S393" s="6" t="s">
+      <c r="S393" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24213,7 +24230,7 @@
       <c r="R394" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S394" s="6" t="s">
+      <c r="S394" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24265,7 +24282,7 @@
       <c r="R395" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S395" s="6" t="s">
+      <c r="S395" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24317,7 +24334,7 @@
       <c r="R396" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S396" s="6" t="s">
+      <c r="S396" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24372,7 +24389,7 @@
       <c r="R397" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S397" s="6" t="s">
+      <c r="S397" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24424,7 +24441,7 @@
       <c r="R398" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S398" s="6" t="s">
+      <c r="S398" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24476,7 +24493,7 @@
       <c r="R399" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S399" s="6" t="s">
+      <c r="S399" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24528,7 +24545,7 @@
       <c r="R400" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S400" s="6" t="s">
+      <c r="S400" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24583,7 +24600,7 @@
       <c r="R401" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S401" s="6" t="s">
+      <c r="S401" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24635,7 +24652,7 @@
       <c r="R402" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S402" s="6" t="s">
+      <c r="S402" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24687,7 +24704,7 @@
       <c r="R403" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S403" s="6" t="s">
+      <c r="S403" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24739,7 +24756,7 @@
       <c r="R404" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S404" s="6" t="s">
+      <c r="S404" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24794,7 +24811,7 @@
       <c r="R405" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S405" s="6" t="s">
+      <c r="S405" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24846,7 +24863,7 @@
       <c r="R406" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S406" s="6" t="s">
+      <c r="S406" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24898,7 +24915,7 @@
       <c r="R407" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S407" s="6" t="s">
+      <c r="S407" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -24950,7 +24967,7 @@
       <c r="R408" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S408" s="6" t="s">
+      <c r="S408" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25005,7 +25022,7 @@
       <c r="R409" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S409" s="6" t="s">
+      <c r="S409" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25057,7 +25074,7 @@
       <c r="R410" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S410" s="6" t="s">
+      <c r="S410" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25109,7 +25126,7 @@
       <c r="R411" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S411" s="6" t="s">
+      <c r="S411" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25161,7 +25178,7 @@
       <c r="R412" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S412" s="6" t="s">
+      <c r="S412" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25216,7 +25233,7 @@
       <c r="R413" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S413" s="6" t="s">
+      <c r="S413" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25268,7 +25285,7 @@
       <c r="R414" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S414" s="6" t="s">
+      <c r="S414" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25320,7 +25337,7 @@
       <c r="R415" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S415" s="6" t="s">
+      <c r="S415" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25372,7 +25389,7 @@
       <c r="R416" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S416" s="6" t="s">
+      <c r="S416" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25427,7 +25444,7 @@
       <c r="R417" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S417" s="6" t="s">
+      <c r="S417" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25479,7 +25496,7 @@
       <c r="R418" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S418" s="6" t="s">
+      <c r="S418" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25531,7 +25548,7 @@
       <c r="R419" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S419" s="6" t="s">
+      <c r="S419" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25583,7 +25600,7 @@
       <c r="R420" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S420" s="6" t="s">
+      <c r="S420" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25638,7 +25655,7 @@
       <c r="R421" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S421" s="6" t="s">
+      <c r="S421" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25690,7 +25707,7 @@
       <c r="R422" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S422" s="6" t="s">
+      <c r="S422" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25742,7 +25759,7 @@
       <c r="R423" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S423" s="6" t="s">
+      <c r="S423" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25794,7 +25811,7 @@
       <c r="R424" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S424" s="6" t="s">
+      <c r="S424" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25849,7 +25866,7 @@
       <c r="R425" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S425" s="6" t="s">
+      <c r="S425" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25901,7 +25918,7 @@
       <c r="R426" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S426" s="6" t="s">
+      <c r="S426" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -25953,7 +25970,7 @@
       <c r="R427" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S427" s="6" t="s">
+      <c r="S427" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26005,7 +26022,7 @@
       <c r="R428" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S428" s="6" t="s">
+      <c r="S428" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26060,7 +26077,7 @@
       <c r="R429" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S429" s="6" t="s">
+      <c r="S429" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26112,7 +26129,7 @@
       <c r="R430" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S430" s="6" t="s">
+      <c r="S430" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26164,7 +26181,7 @@
       <c r="R431" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S431" s="6" t="s">
+      <c r="S431" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26216,7 +26233,7 @@
       <c r="R432" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S432" s="6" t="s">
+      <c r="S432" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26271,7 +26288,7 @@
       <c r="R433" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S433" s="6" t="s">
+      <c r="S433" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26323,7 +26340,7 @@
       <c r="R434" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S434" s="6" t="s">
+      <c r="S434" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26375,7 +26392,7 @@
       <c r="R435" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S435" s="6" t="s">
+      <c r="S435" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26427,7 +26444,7 @@
       <c r="R436" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S436" s="6" t="s">
+      <c r="S436" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26482,7 +26499,7 @@
       <c r="R437" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S437" s="6" t="s">
+      <c r="S437" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26534,7 +26551,7 @@
       <c r="R438" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S438" s="6" t="s">
+      <c r="S438" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26586,7 +26603,7 @@
       <c r="R439" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S439" s="6" t="s">
+      <c r="S439" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26638,7 +26655,7 @@
       <c r="R440" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S440" s="6" t="s">
+      <c r="S440" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26693,7 +26710,7 @@
       <c r="R441" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S441" s="6" t="s">
+      <c r="S441" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26745,7 +26762,7 @@
       <c r="R442" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S442" s="6" t="s">
+      <c r="S442" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26797,7 +26814,7 @@
       <c r="R443" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S443" s="6" t="s">
+      <c r="S443" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26849,7 +26866,7 @@
       <c r="R444" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S444" s="6" t="s">
+      <c r="S444" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26904,7 +26921,7 @@
       <c r="R445" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S445" s="6" t="s">
+      <c r="S445" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -26956,7 +26973,7 @@
       <c r="R446" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S446" s="6" t="s">
+      <c r="S446" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27008,7 +27025,7 @@
       <c r="R447" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S447" s="6" t="s">
+      <c r="S447" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27060,7 +27077,7 @@
       <c r="R448" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S448" s="6" t="s">
+      <c r="S448" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27115,7 +27132,7 @@
       <c r="R449" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S449" s="6" t="s">
+      <c r="S449" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27167,7 +27184,7 @@
       <c r="R450" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S450" s="6" t="s">
+      <c r="S450" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27219,7 +27236,7 @@
       <c r="R451" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S451" s="6" t="s">
+      <c r="S451" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27271,7 +27288,7 @@
       <c r="R452" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S452" s="6" t="s">
+      <c r="S452" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27326,7 +27343,7 @@
       <c r="R453" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S453" s="6" t="s">
+      <c r="S453" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27378,7 +27395,7 @@
       <c r="R454" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S454" s="6" t="s">
+      <c r="S454" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27430,7 +27447,7 @@
       <c r="R455" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S455" s="6" t="s">
+      <c r="S455" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27482,7 +27499,7 @@
       <c r="R456" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S456" s="6" t="s">
+      <c r="S456" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27537,7 +27554,7 @@
       <c r="R457" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S457" s="6" t="s">
+      <c r="S457" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27589,7 +27606,7 @@
       <c r="R458" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S458" s="6" t="s">
+      <c r="S458" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27641,7 +27658,7 @@
       <c r="R459" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S459" s="6" t="s">
+      <c r="S459" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27693,7 +27710,7 @@
       <c r="R460" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S460" s="6" t="s">
+      <c r="S460" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27748,7 +27765,7 @@
       <c r="R461" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S461" s="6" t="s">
+      <c r="S461" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27800,7 +27817,7 @@
       <c r="R462" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S462" s="6" t="s">
+      <c r="S462" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27852,7 +27869,7 @@
       <c r="R463" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S463" s="6" t="s">
+      <c r="S463" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27904,7 +27921,7 @@
       <c r="R464" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S464" s="6" t="s">
+      <c r="S464" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -27959,7 +27976,7 @@
       <c r="R465" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S465" s="6" t="s">
+      <c r="S465" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28011,7 +28028,7 @@
       <c r="R466" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S466" s="6" t="s">
+      <c r="S466" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28063,7 +28080,7 @@
       <c r="R467" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S467" s="6" t="s">
+      <c r="S467" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28115,7 +28132,7 @@
       <c r="R468" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S468" s="6" t="s">
+      <c r="S468" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28170,7 +28187,7 @@
       <c r="R469" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S469" s="6" t="s">
+      <c r="S469" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28222,7 +28239,7 @@
       <c r="R470" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S470" s="6" t="s">
+      <c r="S470" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28274,7 +28291,7 @@
       <c r="R471" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S471" s="6" t="s">
+      <c r="S471" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28326,7 +28343,7 @@
       <c r="R472" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S472" s="6" t="s">
+      <c r="S472" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28381,7 +28398,7 @@
       <c r="R473" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S473" s="6" t="s">
+      <c r="S473" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28433,7 +28450,7 @@
       <c r="R474" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S474" s="6" t="s">
+      <c r="S474" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28485,7 +28502,7 @@
       <c r="R475" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S475" s="6" t="s">
+      <c r="S475" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28537,7 +28554,7 @@
       <c r="R476" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S476" s="6" t="s">
+      <c r="S476" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28592,7 +28609,7 @@
       <c r="R477" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S477" s="6" t="s">
+      <c r="S477" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28644,7 +28661,7 @@
       <c r="R478" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S478" s="6" t="s">
+      <c r="S478" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28696,7 +28713,7 @@
       <c r="R479" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S479" s="6" t="s">
+      <c r="S479" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28748,7 +28765,7 @@
       <c r="R480" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S480" s="6" t="s">
+      <c r="S480" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28803,7 +28820,7 @@
       <c r="R481" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S481" s="6" t="s">
+      <c r="S481" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28855,7 +28872,7 @@
       <c r="R482" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S482" s="6" t="s">
+      <c r="S482" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28907,7 +28924,7 @@
       <c r="R483" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S483" s="6" t="s">
+      <c r="S483" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -28959,7 +28976,7 @@
       <c r="R484" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S484" s="6" t="s">
+      <c r="S484" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29014,7 +29031,7 @@
       <c r="R485" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S485" s="6" t="s">
+      <c r="S485" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29066,7 +29083,7 @@
       <c r="R486" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S486" s="6" t="s">
+      <c r="S486" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29118,7 +29135,7 @@
       <c r="R487" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S487" s="6" t="s">
+      <c r="S487" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29170,7 +29187,7 @@
       <c r="R488" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S488" s="6" t="s">
+      <c r="S488" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29225,7 +29242,7 @@
       <c r="R489" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S489" s="6" t="s">
+      <c r="S489" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29277,7 +29294,7 @@
       <c r="R490" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S490" s="6" t="s">
+      <c r="S490" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29329,7 +29346,7 @@
       <c r="R491" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S491" s="6" t="s">
+      <c r="S491" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29381,7 +29398,7 @@
       <c r="R492" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S492" s="6" t="s">
+      <c r="S492" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29436,7 +29453,7 @@
       <c r="R493" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S493" s="6" t="s">
+      <c r="S493" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29488,7 +29505,7 @@
       <c r="R494" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S494" s="6" t="s">
+      <c r="S494" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29540,7 +29557,7 @@
       <c r="R495" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S495" s="6" t="s">
+      <c r="S495" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29592,7 +29609,7 @@
       <c r="R496" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S496" s="6" t="s">
+      <c r="S496" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29647,7 +29664,7 @@
       <c r="R497" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S497" s="6" t="s">
+      <c r="S497" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29699,7 +29716,7 @@
       <c r="R498" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S498" s="6" t="s">
+      <c r="S498" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29751,7 +29768,7 @@
       <c r="R499" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S499" s="6" t="s">
+      <c r="S499" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29803,7 +29820,7 @@
       <c r="R500" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S500" s="6" t="s">
+      <c r="S500" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29858,7 +29875,7 @@
       <c r="R501" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S501" s="6" t="s">
+      <c r="S501" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29910,7 +29927,7 @@
       <c r="R502" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S502" s="6" t="s">
+      <c r="S502" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -29962,7 +29979,7 @@
       <c r="R503" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S503" s="6" t="s">
+      <c r="S503" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30014,7 +30031,7 @@
       <c r="R504" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S504" s="6" t="s">
+      <c r="S504" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30069,7 +30086,7 @@
       <c r="R505" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S505" s="6" t="s">
+      <c r="S505" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30121,7 +30138,7 @@
       <c r="R506" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S506" s="6" t="s">
+      <c r="S506" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30173,7 +30190,7 @@
       <c r="R507" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S507" s="6" t="s">
+      <c r="S507" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30225,7 +30242,7 @@
       <c r="R508" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S508" s="6" t="s">
+      <c r="S508" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30280,7 +30297,7 @@
       <c r="R509" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S509" s="6" t="s">
+      <c r="S509" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30332,7 +30349,7 @@
       <c r="R510" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S510" s="6" t="s">
+      <c r="S510" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30384,7 +30401,7 @@
       <c r="R511" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S511" s="6" t="s">
+      <c r="S511" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30436,7 +30453,7 @@
       <c r="R512" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S512" s="6" t="s">
+      <c r="S512" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30491,7 +30508,7 @@
       <c r="R513" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S513" s="6" t="s">
+      <c r="S513" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30543,7 +30560,7 @@
       <c r="R514" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S514" s="6" t="s">
+      <c r="S514" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30595,7 +30612,7 @@
       <c r="R515" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S515" s="6" t="s">
+      <c r="S515" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30647,7 +30664,7 @@
       <c r="R516" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S516" s="6" t="s">
+      <c r="S516" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30702,7 +30719,7 @@
       <c r="R517" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S517" s="6" t="s">
+      <c r="S517" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30754,7 +30771,7 @@
       <c r="R518" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S518" s="6" t="s">
+      <c r="S518" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30806,7 +30823,7 @@
       <c r="R519" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S519" s="6" t="s">
+      <c r="S519" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30858,7 +30875,7 @@
       <c r="R520" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S520" s="6" t="s">
+      <c r="S520" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30913,7 +30930,7 @@
       <c r="R521" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S521" s="6" t="s">
+      <c r="S521" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -30965,7 +30982,7 @@
       <c r="R522" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S522" s="6" t="s">
+      <c r="S522" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31017,7 +31034,7 @@
       <c r="R523" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S523" s="6" t="s">
+      <c r="S523" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31069,7 +31086,7 @@
       <c r="R524" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S524" s="6" t="s">
+      <c r="S524" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31124,7 +31141,7 @@
       <c r="R525" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S525" s="6" t="s">
+      <c r="S525" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31176,7 +31193,7 @@
       <c r="R526" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S526" s="6" t="s">
+      <c r="S526" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31228,7 +31245,7 @@
       <c r="R527" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S527" s="6" t="s">
+      <c r="S527" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31280,7 +31297,7 @@
       <c r="R528" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S528" s="6" t="s">
+      <c r="S528" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31335,7 +31352,7 @@
       <c r="R529" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S529" s="6" t="s">
+      <c r="S529" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31387,7 +31404,7 @@
       <c r="R530" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S530" s="6" t="s">
+      <c r="S530" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31439,7 +31456,7 @@
       <c r="R531" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S531" s="6" t="s">
+      <c r="S531" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31491,7 +31508,7 @@
       <c r="R532" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S532" s="6" t="s">
+      <c r="S532" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31546,7 +31563,7 @@
       <c r="R533" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S533" s="6" t="s">
+      <c r="S533" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31598,7 +31615,7 @@
       <c r="R534" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S534" s="6" t="s">
+      <c r="S534" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31650,7 +31667,7 @@
       <c r="R535" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S535" s="6" t="s">
+      <c r="S535" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31702,7 +31719,7 @@
       <c r="R536" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S536" s="6" t="s">
+      <c r="S536" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31757,7 +31774,7 @@
       <c r="R537" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S537" s="6" t="s">
+      <c r="S537" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31809,7 +31826,7 @@
       <c r="R538" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S538" s="6" t="s">
+      <c r="S538" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31861,7 +31878,7 @@
       <c r="R539" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S539" s="6" t="s">
+      <c r="S539" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31913,7 +31930,7 @@
       <c r="R540" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S540" s="6" t="s">
+      <c r="S540" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -31968,7 +31985,7 @@
       <c r="R541" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S541" s="6" t="s">
+      <c r="S541" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32020,7 +32037,7 @@
       <c r="R542" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S542" s="6" t="s">
+      <c r="S542" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32072,7 +32089,7 @@
       <c r="R543" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S543" s="6" t="s">
+      <c r="S543" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32124,7 +32141,7 @@
       <c r="R544" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S544" s="6" t="s">
+      <c r="S544" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32179,7 +32196,7 @@
       <c r="R545" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S545" s="6" t="s">
+      <c r="S545" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32231,7 +32248,7 @@
       <c r="R546" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S546" s="6" t="s">
+      <c r="S546" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32283,7 +32300,7 @@
       <c r="R547" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S547" s="6" t="s">
+      <c r="S547" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32335,7 +32352,7 @@
       <c r="R548" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S548" s="6" t="s">
+      <c r="S548" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32390,7 +32407,7 @@
       <c r="R549" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S549" s="6" t="s">
+      <c r="S549" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32442,7 +32459,7 @@
       <c r="R550" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S550" s="6" t="s">
+      <c r="S550" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32494,7 +32511,7 @@
       <c r="R551" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S551" s="6" t="s">
+      <c r="S551" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32546,7 +32563,7 @@
       <c r="R552" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S552" s="6" t="s">
+      <c r="S552" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32601,7 +32618,7 @@
       <c r="R553" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S553" s="6" t="s">
+      <c r="S553" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32653,7 +32670,7 @@
       <c r="R554" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S554" s="6" t="s">
+      <c r="S554" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32705,7 +32722,7 @@
       <c r="R555" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S555" s="6" t="s">
+      <c r="S555" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32757,7 +32774,7 @@
       <c r="R556" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S556" s="6" t="s">
+      <c r="S556" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32812,7 +32829,7 @@
       <c r="R557" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S557" s="6" t="s">
+      <c r="S557" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32864,7 +32881,7 @@
       <c r="R558" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S558" s="6" t="s">
+      <c r="S558" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32916,7 +32933,7 @@
       <c r="R559" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S559" s="6" t="s">
+      <c r="S559" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -32968,7 +32985,7 @@
       <c r="R560" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S560" s="6" t="s">
+      <c r="S560" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33023,7 +33040,7 @@
       <c r="R561" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S561" s="6" t="s">
+      <c r="S561" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33075,7 +33092,7 @@
       <c r="R562" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S562" s="6" t="s">
+      <c r="S562" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33127,7 +33144,7 @@
       <c r="R563" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S563" s="6" t="s">
+      <c r="S563" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33179,7 +33196,7 @@
       <c r="R564" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S564" s="6" t="s">
+      <c r="S564" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33234,7 +33251,7 @@
       <c r="R565" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S565" s="6" t="s">
+      <c r="S565" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33286,7 +33303,7 @@
       <c r="R566" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S566" s="6" t="s">
+      <c r="S566" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33308,7 +33325,7 @@
       <c r="P567" s="41"/>
       <c r="Q567" s="41"/>
       <c r="R567" s="41"/>
-      <c r="S567" s="6" t="s">
+      <c r="S567" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33330,7 +33347,7 @@
       <c r="P568" s="43"/>
       <c r="Q568" s="43"/>
       <c r="R568" s="43"/>
-      <c r="S568" s="6" t="s">
+      <c r="S568" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33355,7 +33372,7 @@
       <c r="P569" s="44"/>
       <c r="Q569" s="44"/>
       <c r="R569" s="44"/>
-      <c r="S569" s="6" t="s">
+      <c r="S569" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33377,7 +33394,7 @@
       <c r="P570" s="43"/>
       <c r="Q570" s="43"/>
       <c r="R570" s="43"/>
-      <c r="S570" s="6" t="s">
+      <c r="S570" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33399,7 +33416,7 @@
       <c r="P571" s="41"/>
       <c r="Q571" s="41"/>
       <c r="R571" s="41"/>
-      <c r="S571" s="6" t="s">
+      <c r="S571" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33421,7 +33438,7 @@
       <c r="P572" s="43"/>
       <c r="Q572" s="43"/>
       <c r="R572" s="43"/>
-      <c r="S572" s="6" t="s">
+      <c r="S572" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33446,7 +33463,7 @@
       <c r="P573" s="44"/>
       <c r="Q573" s="44"/>
       <c r="R573" s="44"/>
-      <c r="S573" s="6" t="s">
+      <c r="S573" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33468,7 +33485,7 @@
       <c r="P574" s="43"/>
       <c r="Q574" s="43"/>
       <c r="R574" s="43"/>
-      <c r="S574" s="6" t="s">
+      <c r="S574" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33490,7 +33507,7 @@
       <c r="P575" s="41"/>
       <c r="Q575" s="41"/>
       <c r="R575" s="41"/>
-      <c r="S575" s="6" t="s">
+      <c r="S575" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33512,7 +33529,7 @@
       <c r="P576" s="43"/>
       <c r="Q576" s="43"/>
       <c r="R576" s="43"/>
-      <c r="S576" s="6" t="s">
+      <c r="S576" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33537,7 +33554,7 @@
       <c r="P577" s="44"/>
       <c r="Q577" s="44"/>
       <c r="R577" s="44"/>
-      <c r="S577" s="6" t="s">
+      <c r="S577" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33559,7 +33576,7 @@
       <c r="P578" s="43"/>
       <c r="Q578" s="43"/>
       <c r="R578" s="43"/>
-      <c r="S578" s="6" t="s">
+      <c r="S578" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33581,7 +33598,7 @@
       <c r="P579" s="41"/>
       <c r="Q579" s="41"/>
       <c r="R579" s="41"/>
-      <c r="S579" s="6" t="s">
+      <c r="S579" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33633,7 +33650,7 @@
       <c r="R580" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S580" s="6" t="s">
+      <c r="S580" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33688,7 +33705,7 @@
       <c r="R581" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S581" s="6" t="s">
+      <c r="S581" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33740,7 +33757,7 @@
       <c r="R582" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S582" s="6" t="s">
+      <c r="S582" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33792,7 +33809,7 @@
       <c r="R583" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S583" s="6" t="s">
+      <c r="S583" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33844,7 +33861,7 @@
       <c r="R584" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S584" s="6" t="s">
+      <c r="S584" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33899,7 +33916,7 @@
       <c r="R585" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S585" s="6" t="s">
+      <c r="S585" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -33951,7 +33968,7 @@
       <c r="R586" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S586" s="6" t="s">
+      <c r="S586" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34003,7 +34020,7 @@
       <c r="R587" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S587" s="6" t="s">
+      <c r="S587" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34055,7 +34072,7 @@
       <c r="R588" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S588" s="6" t="s">
+      <c r="S588" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34110,7 +34127,7 @@
       <c r="R589" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S589" s="6" t="s">
+      <c r="S589" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34162,7 +34179,7 @@
       <c r="R590" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S590" s="6" t="s">
+      <c r="S590" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34214,7 +34231,7 @@
       <c r="R591" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S591" s="6" t="s">
+      <c r="S591" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34266,7 +34283,7 @@
       <c r="R592" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S592" s="6" t="s">
+      <c r="S592" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34321,7 +34338,7 @@
       <c r="R593" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S593" s="6" t="s">
+      <c r="S593" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34373,7 +34390,7 @@
       <c r="R594" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S594" s="6" t="s">
+      <c r="S594" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34425,7 +34442,7 @@
       <c r="R595" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S595" s="6" t="s">
+      <c r="S595" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34477,7 +34494,7 @@
       <c r="R596" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S596" s="6" t="s">
+      <c r="S596" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34532,7 +34549,7 @@
       <c r="R597" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S597" s="6" t="s">
+      <c r="S597" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34584,7 +34601,7 @@
       <c r="R598" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S598" s="6" t="s">
+      <c r="S598" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34636,7 +34653,7 @@
       <c r="R599" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S599" s="6" t="s">
+      <c r="S599" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34688,7 +34705,7 @@
       <c r="R600" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S600" s="6" t="s">
+      <c r="S600" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34743,7 +34760,7 @@
       <c r="R601" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S601" s="6" t="s">
+      <c r="S601" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34795,7 +34812,7 @@
       <c r="R602" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S602" s="6" t="s">
+      <c r="S602" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34847,7 +34864,7 @@
       <c r="R603" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S603" s="6" t="s">
+      <c r="S603" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34899,7 +34916,7 @@
       <c r="R604" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S604" s="6" t="s">
+      <c r="S604" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -34954,7 +34971,7 @@
       <c r="R605" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S605" s="6" t="s">
+      <c r="S605" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35006,7 +35023,7 @@
       <c r="R606" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S606" s="6" t="s">
+      <c r="S606" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35058,7 +35075,7 @@
       <c r="R607" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S607" s="6" t="s">
+      <c r="S607" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35110,7 +35127,7 @@
       <c r="R608" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S608" s="6" t="s">
+      <c r="S608" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35165,7 +35182,7 @@
       <c r="R609" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S609" s="6" t="s">
+      <c r="S609" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35217,7 +35234,7 @@
       <c r="R610" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S610" s="6" t="s">
+      <c r="S610" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35269,7 +35286,7 @@
       <c r="R611" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S611" s="6" t="s">
+      <c r="S611" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35321,7 +35338,7 @@
       <c r="R612" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S612" s="6" t="s">
+      <c r="S612" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35376,7 +35393,7 @@
       <c r="R613" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S613" s="6" t="s">
+      <c r="S613" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35428,7 +35445,7 @@
       <c r="R614" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S614" s="6" t="s">
+      <c r="S614" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35480,7 +35497,7 @@
       <c r="R615" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S615" s="6" t="s">
+      <c r="S615" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35532,7 +35549,7 @@
       <c r="R616" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S616" s="6" t="s">
+      <c r="S616" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35587,7 +35604,7 @@
       <c r="R617" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S617" s="6" t="s">
+      <c r="S617" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35639,7 +35656,7 @@
       <c r="R618" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S618" s="6" t="s">
+      <c r="S618" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35691,7 +35708,7 @@
       <c r="R619" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S619" s="6" t="s">
+      <c r="S619" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35743,7 +35760,7 @@
       <c r="R620" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S620" s="6" t="s">
+      <c r="S620" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35798,7 +35815,7 @@
       <c r="R621" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S621" s="6" t="s">
+      <c r="S621" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35850,7 +35867,7 @@
       <c r="R622" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S622" s="6" t="s">
+      <c r="S622" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35902,7 +35919,7 @@
       <c r="R623" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S623" s="6" t="s">
+      <c r="S623" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -35954,7 +35971,7 @@
       <c r="R624" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S624" s="6" t="s">
+      <c r="S624" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -36009,7 +36026,7 @@
       <c r="R625" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S625" s="6" t="s">
+      <c r="S625" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -36061,7 +36078,7 @@
       <c r="R626" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S626" s="6" t="s">
+      <c r="S626" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -36113,7 +36130,7 @@
       <c r="R627" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S627" s="6" t="s">
+      <c r="S627" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -36165,7 +36182,7 @@
       <c r="R628" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S628" s="6" t="s">
+      <c r="S628" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -36220,7 +36237,7 @@
       <c r="R629" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S629" s="6" t="s">
+      <c r="S629" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -36272,7 +36289,7 @@
       <c r="R630" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S630" s="6" t="s">
+      <c r="S630" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -36324,7 +36341,7 @@
       <c r="R631" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="S631" s="6" t="s">
+      <c r="S631" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -36376,7 +36393,7 @@
       <c r="R632" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S632" s="6" t="s">
+      <c r="S632" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -36431,7 +36448,7 @@
       <c r="R633" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="S633" s="6" t="s">
+      <c r="S633" s="53" t="s">
         <v>32</v>
       </c>
     </row>
@@ -36483,7 +36500,7 @@
       <c r="R634" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="S634" s="6" t="s">
+      <c r="S634" s="53" t="s">
         <v>32</v>
       </c>
     </row>
